--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10273900</v>
+        <v>10303200</v>
       </c>
       <c r="E8" s="3">
-        <v>9746600</v>
+        <v>9774400</v>
       </c>
       <c r="F8" s="3">
-        <v>11895900</v>
+        <v>11929900</v>
       </c>
       <c r="G8" s="3">
-        <v>15740100</v>
+        <v>15785100</v>
       </c>
       <c r="H8" s="3">
-        <v>18629500</v>
+        <v>18682700</v>
       </c>
       <c r="I8" s="3">
-        <v>16050400</v>
+        <v>16096300</v>
       </c>
       <c r="J8" s="3">
-        <v>17173400</v>
+        <v>17222400</v>
       </c>
       <c r="K8" s="3">
         <v>14471700</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7120900</v>
+        <v>7141200</v>
       </c>
       <c r="E9" s="3">
-        <v>7077500</v>
+        <v>7097700</v>
       </c>
       <c r="F9" s="3">
-        <v>8739700</v>
+        <v>8764600</v>
       </c>
       <c r="G9" s="3">
-        <v>12130300</v>
+        <v>12165000</v>
       </c>
       <c r="H9" s="3">
-        <v>12886500</v>
+        <v>12923400</v>
       </c>
       <c r="I9" s="3">
-        <v>11595400</v>
+        <v>11628500</v>
       </c>
       <c r="J9" s="3">
-        <v>10954200</v>
+        <v>10985500</v>
       </c>
       <c r="K9" s="3">
         <v>9568300</v>
@@ -978,25 +978,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3153000</v>
+        <v>3162000</v>
       </c>
       <c r="E10" s="3">
-        <v>2669100</v>
+        <v>2676700</v>
       </c>
       <c r="F10" s="3">
-        <v>3156300</v>
+        <v>3165300</v>
       </c>
       <c r="G10" s="3">
-        <v>3609800</v>
+        <v>3620100</v>
       </c>
       <c r="H10" s="3">
-        <v>5742900</v>
+        <v>5759300</v>
       </c>
       <c r="I10" s="3">
-        <v>4455000</v>
+        <v>4467700</v>
       </c>
       <c r="J10" s="3">
-        <v>6219200</v>
+        <v>6237000</v>
       </c>
       <c r="K10" s="3">
         <v>4903400</v>
@@ -1104,22 +1104,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>41200</v>
+        <v>41300</v>
       </c>
       <c r="E12" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="F12" s="3">
-        <v>46700</v>
+        <v>46800</v>
       </c>
       <c r="G12" s="3">
-        <v>115000</v>
+        <v>115300</v>
       </c>
       <c r="H12" s="3">
-        <v>60800</v>
+        <v>60900</v>
       </c>
       <c r="I12" s="3">
-        <v>84600</v>
+        <v>84900</v>
       </c>
       <c r="J12" s="3">
         <v>10900</v>
@@ -1291,7 +1291,7 @@
         <v>-14100</v>
       </c>
       <c r="E14" s="3">
-        <v>76000</v>
+        <v>76200</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1303,10 +1303,10 @@
         <v>6500</v>
       </c>
       <c r="I14" s="3">
-        <v>-171400</v>
+        <v>-171900</v>
       </c>
       <c r="J14" s="3">
-        <v>1099100</v>
+        <v>1102200</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1380,25 +1380,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>708500</v>
+        <v>710500</v>
       </c>
       <c r="E15" s="3">
-        <v>639100</v>
+        <v>640900</v>
       </c>
       <c r="F15" s="3">
-        <v>661900</v>
+        <v>663700</v>
       </c>
       <c r="G15" s="3">
-        <v>896200</v>
+        <v>898800</v>
       </c>
       <c r="H15" s="3">
-        <v>683600</v>
+        <v>685500</v>
       </c>
       <c r="I15" s="3">
-        <v>182300</v>
+        <v>182800</v>
       </c>
       <c r="J15" s="3">
-        <v>644500</v>
+        <v>646300</v>
       </c>
       <c r="K15" s="3">
         <v>2002300</v>
@@ -1503,25 +1503,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8894800</v>
+        <v>8920200</v>
       </c>
       <c r="E17" s="3">
-        <v>8544400</v>
+        <v>8568800</v>
       </c>
       <c r="F17" s="3">
-        <v>10495200</v>
+        <v>10525200</v>
       </c>
       <c r="G17" s="3">
-        <v>13847900</v>
+        <v>13887400</v>
       </c>
       <c r="H17" s="3">
-        <v>14983900</v>
+        <v>15026700</v>
       </c>
       <c r="I17" s="3">
-        <v>12445000</v>
+        <v>12480500</v>
       </c>
       <c r="J17" s="3">
-        <v>15062000</v>
+        <v>15105000</v>
       </c>
       <c r="K17" s="3">
         <v>12857400</v>
@@ -1595,25 +1595,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1379000</v>
+        <v>1383000</v>
       </c>
       <c r="E18" s="3">
-        <v>1202200</v>
+        <v>1205600</v>
       </c>
       <c r="F18" s="3">
-        <v>1400700</v>
+        <v>1404700</v>
       </c>
       <c r="G18" s="3">
-        <v>1892200</v>
+        <v>1897600</v>
       </c>
       <c r="H18" s="3">
-        <v>3645600</v>
+        <v>3656000</v>
       </c>
       <c r="I18" s="3">
-        <v>3605500</v>
+        <v>3615800</v>
       </c>
       <c r="J18" s="3">
-        <v>2111400</v>
+        <v>2117400</v>
       </c>
       <c r="K18" s="3">
         <v>1614200</v>
@@ -1721,25 +1721,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>180100</v>
+        <v>180600</v>
       </c>
       <c r="E20" s="3">
-        <v>-194200</v>
+        <v>-194800</v>
       </c>
       <c r="F20" s="3">
-        <v>199600</v>
+        <v>200200</v>
       </c>
       <c r="G20" s="3">
         <v>32600</v>
       </c>
       <c r="H20" s="3">
-        <v>61800</v>
+        <v>62000</v>
       </c>
       <c r="I20" s="3">
-        <v>488300</v>
+        <v>489600</v>
       </c>
       <c r="J20" s="3">
-        <v>292900</v>
+        <v>293800</v>
       </c>
       <c r="K20" s="3">
         <v>139800</v>
@@ -1813,25 +1813,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2272000</v>
+        <v>2278500</v>
       </c>
       <c r="E21" s="3">
-        <v>1736000</v>
+        <v>1741000</v>
       </c>
       <c r="F21" s="3">
-        <v>2295900</v>
+        <v>2302400</v>
       </c>
       <c r="G21" s="3">
-        <v>2906700</v>
+        <v>2915000</v>
       </c>
       <c r="H21" s="3">
-        <v>4435500</v>
+        <v>4448200</v>
       </c>
       <c r="I21" s="3">
-        <v>4621000</v>
+        <v>4634200</v>
       </c>
       <c r="J21" s="3">
-        <v>3060800</v>
+        <v>3069500</v>
       </c>
       <c r="K21" s="3">
         <v>3876700</v>
@@ -1905,25 +1905,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>123700</v>
+        <v>124000</v>
       </c>
       <c r="E22" s="3">
-        <v>99800</v>
+        <v>100100</v>
       </c>
       <c r="F22" s="3">
-        <v>110700</v>
+        <v>111000</v>
       </c>
       <c r="G22" s="3">
-        <v>116100</v>
+        <v>116400</v>
       </c>
       <c r="H22" s="3">
-        <v>111800</v>
+        <v>112100</v>
       </c>
       <c r="I22" s="3">
-        <v>120400</v>
+        <v>120800</v>
       </c>
       <c r="J22" s="3">
-        <v>103100</v>
+        <v>103400</v>
       </c>
       <c r="K22" s="3">
         <v>90000</v>
@@ -1997,25 +1997,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1435500</v>
+        <v>1439600</v>
       </c>
       <c r="E23" s="3">
-        <v>908100</v>
+        <v>910700</v>
       </c>
       <c r="F23" s="3">
-        <v>1489700</v>
+        <v>1494000</v>
       </c>
       <c r="G23" s="3">
-        <v>1808700</v>
+        <v>1813900</v>
       </c>
       <c r="H23" s="3">
-        <v>3595700</v>
+        <v>3606000</v>
       </c>
       <c r="I23" s="3">
-        <v>3973300</v>
+        <v>3984600</v>
       </c>
       <c r="J23" s="3">
-        <v>2301300</v>
+        <v>2307900</v>
       </c>
       <c r="K23" s="3">
         <v>1664100</v>
@@ -2089,25 +2089,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>695500</v>
+        <v>697500</v>
       </c>
       <c r="E24" s="3">
-        <v>554400</v>
+        <v>556000</v>
       </c>
       <c r="F24" s="3">
-        <v>847400</v>
+        <v>849800</v>
       </c>
       <c r="G24" s="3">
-        <v>1323700</v>
+        <v>1327500</v>
       </c>
       <c r="H24" s="3">
-        <v>2121200</v>
+        <v>2127200</v>
       </c>
       <c r="I24" s="3">
-        <v>1247800</v>
+        <v>1251300</v>
       </c>
       <c r="J24" s="3">
-        <v>1372500</v>
+        <v>1376400</v>
       </c>
       <c r="K24" s="3">
         <v>930200</v>
@@ -2273,25 +2273,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>740000</v>
+        <v>742100</v>
       </c>
       <c r="E26" s="3">
-        <v>353700</v>
+        <v>354700</v>
       </c>
       <c r="F26" s="3">
-        <v>642300</v>
+        <v>644200</v>
       </c>
       <c r="G26" s="3">
-        <v>485000</v>
+        <v>486400</v>
       </c>
       <c r="H26" s="3">
-        <v>1474500</v>
+        <v>1478700</v>
       </c>
       <c r="I26" s="3">
-        <v>2725500</v>
+        <v>2733300</v>
       </c>
       <c r="J26" s="3">
-        <v>928800</v>
+        <v>931400</v>
       </c>
       <c r="K26" s="3">
         <v>733900</v>
@@ -2365,25 +2365,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>512100</v>
+        <v>513600</v>
       </c>
       <c r="E27" s="3">
-        <v>412300</v>
+        <v>413500</v>
       </c>
       <c r="F27" s="3">
-        <v>423200</v>
+        <v>424400</v>
       </c>
       <c r="G27" s="3">
-        <v>334200</v>
+        <v>335100</v>
       </c>
       <c r="H27" s="3">
-        <v>903800</v>
+        <v>906400</v>
       </c>
       <c r="I27" s="3">
-        <v>2112500</v>
+        <v>2118500</v>
       </c>
       <c r="J27" s="3">
-        <v>592400</v>
+        <v>594100</v>
       </c>
       <c r="K27" s="3">
         <v>583200</v>
@@ -2825,25 +2825,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-180100</v>
+        <v>-180600</v>
       </c>
       <c r="E32" s="3">
-        <v>194200</v>
+        <v>194800</v>
       </c>
       <c r="F32" s="3">
-        <v>-199600</v>
+        <v>-200200</v>
       </c>
       <c r="G32" s="3">
         <v>-32600</v>
       </c>
       <c r="H32" s="3">
-        <v>-61800</v>
+        <v>-62000</v>
       </c>
       <c r="I32" s="3">
-        <v>-488300</v>
+        <v>-489600</v>
       </c>
       <c r="J32" s="3">
-        <v>-292900</v>
+        <v>-293800</v>
       </c>
       <c r="K32" s="3">
         <v>-139800</v>
@@ -2917,25 +2917,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>512100</v>
+        <v>513600</v>
       </c>
       <c r="E33" s="3">
-        <v>412300</v>
+        <v>413500</v>
       </c>
       <c r="F33" s="3">
-        <v>423200</v>
+        <v>424400</v>
       </c>
       <c r="G33" s="3">
-        <v>334200</v>
+        <v>335100</v>
       </c>
       <c r="H33" s="3">
-        <v>903800</v>
+        <v>906400</v>
       </c>
       <c r="I33" s="3">
-        <v>2112500</v>
+        <v>2118500</v>
       </c>
       <c r="J33" s="3">
-        <v>592400</v>
+        <v>594100</v>
       </c>
       <c r="K33" s="3">
         <v>583200</v>
@@ -3101,25 +3101,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>512100</v>
+        <v>513600</v>
       </c>
       <c r="E35" s="3">
-        <v>412300</v>
+        <v>413500</v>
       </c>
       <c r="F35" s="3">
-        <v>423200</v>
+        <v>424400</v>
       </c>
       <c r="G35" s="3">
-        <v>334200</v>
+        <v>335100</v>
       </c>
       <c r="H35" s="3">
-        <v>903800</v>
+        <v>906400</v>
       </c>
       <c r="I35" s="3">
-        <v>2112500</v>
+        <v>2118500</v>
       </c>
       <c r="J35" s="3">
-        <v>592400</v>
+        <v>594100</v>
       </c>
       <c r="K35" s="3">
         <v>583200</v>
@@ -3358,25 +3358,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8445600</v>
+        <v>8469800</v>
       </c>
       <c r="E41" s="3">
-        <v>6786700</v>
+        <v>6806100</v>
       </c>
       <c r="F41" s="3">
-        <v>10264100</v>
+        <v>10293400</v>
       </c>
       <c r="G41" s="3">
-        <v>8777700</v>
+        <v>8802700</v>
       </c>
       <c r="H41" s="3">
-        <v>8254700</v>
+        <v>8278300</v>
       </c>
       <c r="I41" s="3">
-        <v>7098100</v>
+        <v>7118400</v>
       </c>
       <c r="J41" s="3">
-        <v>6531700</v>
+        <v>6550400</v>
       </c>
       <c r="K41" s="3">
         <v>5474700</v>
@@ -3450,25 +3450,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2422800</v>
+        <v>2429700</v>
       </c>
       <c r="E42" s="3">
-        <v>2314300</v>
+        <v>2320900</v>
       </c>
       <c r="F42" s="3">
-        <v>2189500</v>
+        <v>2195800</v>
       </c>
       <c r="G42" s="3">
-        <v>4263000</v>
+        <v>4275100</v>
       </c>
       <c r="H42" s="3">
-        <v>8103900</v>
+        <v>8127000</v>
       </c>
       <c r="I42" s="3">
-        <v>8376200</v>
+        <v>8400100</v>
       </c>
       <c r="J42" s="3">
-        <v>7982300</v>
+        <v>8005200</v>
       </c>
       <c r="K42" s="3">
         <v>5580900</v>
@@ -3542,25 +3542,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3368900</v>
+        <v>3378600</v>
       </c>
       <c r="E43" s="3">
-        <v>3018500</v>
+        <v>3027100</v>
       </c>
       <c r="F43" s="3">
-        <v>4327000</v>
+        <v>4339300</v>
       </c>
       <c r="G43" s="3">
-        <v>4686100</v>
+        <v>4699500</v>
       </c>
       <c r="H43" s="3">
-        <v>6249600</v>
+        <v>6267500</v>
       </c>
       <c r="I43" s="3">
-        <v>5745100</v>
+        <v>5761500</v>
       </c>
       <c r="J43" s="3">
-        <v>5843800</v>
+        <v>5860500</v>
       </c>
       <c r="K43" s="3">
         <v>5014000</v>
@@ -3634,25 +3634,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4343300</v>
+        <v>4355700</v>
       </c>
       <c r="E44" s="3">
-        <v>4396400</v>
+        <v>4409000</v>
       </c>
       <c r="F44" s="3">
-        <v>4371500</v>
+        <v>4384000</v>
       </c>
       <c r="G44" s="3">
-        <v>5244900</v>
+        <v>5259900</v>
       </c>
       <c r="H44" s="3">
-        <v>5774400</v>
+        <v>5790900</v>
       </c>
       <c r="I44" s="3">
-        <v>5573600</v>
+        <v>5589600</v>
       </c>
       <c r="J44" s="3">
-        <v>4244500</v>
+        <v>4256600</v>
       </c>
       <c r="K44" s="3">
         <v>3414900</v>
@@ -3726,25 +3726,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1006900</v>
+        <v>1009800</v>
       </c>
       <c r="E45" s="3">
-        <v>940700</v>
+        <v>943400</v>
       </c>
       <c r="F45" s="3">
-        <v>1037300</v>
+        <v>1040200</v>
       </c>
       <c r="G45" s="3">
-        <v>1298700</v>
+        <v>1302500</v>
       </c>
       <c r="H45" s="3">
-        <v>1026400</v>
+        <v>1029300</v>
       </c>
       <c r="I45" s="3">
-        <v>802900</v>
+        <v>805200</v>
       </c>
       <c r="J45" s="3">
-        <v>766000</v>
+        <v>768200</v>
       </c>
       <c r="K45" s="3">
         <v>674300</v>
@@ -3818,25 +3818,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19587500</v>
+        <v>19643500</v>
       </c>
       <c r="E46" s="3">
-        <v>17456600</v>
+        <v>17506400</v>
       </c>
       <c r="F46" s="3">
-        <v>22189300</v>
+        <v>22252700</v>
       </c>
       <c r="G46" s="3">
-        <v>24270400</v>
+        <v>24339700</v>
       </c>
       <c r="H46" s="3">
-        <v>29408900</v>
+        <v>29493000</v>
       </c>
       <c r="I46" s="3">
-        <v>27595900</v>
+        <v>27674700</v>
       </c>
       <c r="J46" s="3">
-        <v>25368400</v>
+        <v>25440900</v>
       </c>
       <c r="K46" s="3">
         <v>20158800</v>
@@ -3910,25 +3910,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9415600</v>
+        <v>9442500</v>
       </c>
       <c r="E47" s="3">
-        <v>9375500</v>
+        <v>9402300</v>
       </c>
       <c r="F47" s="3">
-        <v>9550200</v>
+        <v>9577500</v>
       </c>
       <c r="G47" s="3">
-        <v>10082900</v>
+        <v>10111700</v>
       </c>
       <c r="H47" s="3">
-        <v>12335400</v>
+        <v>12370600</v>
       </c>
       <c r="I47" s="3">
-        <v>11543300</v>
+        <v>11576300</v>
       </c>
       <c r="J47" s="3">
-        <v>11773300</v>
+        <v>11807000</v>
       </c>
       <c r="K47" s="3">
         <v>11509900</v>
@@ -4002,25 +4002,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22014700</v>
+        <v>22077500</v>
       </c>
       <c r="E48" s="3">
-        <v>22199100</v>
+        <v>22262500</v>
       </c>
       <c r="F48" s="3">
-        <v>21046800</v>
+        <v>21107000</v>
       </c>
       <c r="G48" s="3">
-        <v>20958900</v>
+        <v>21018800</v>
       </c>
       <c r="H48" s="3">
-        <v>20846100</v>
+        <v>20905700</v>
       </c>
       <c r="I48" s="3">
-        <v>20688800</v>
+        <v>20747900</v>
       </c>
       <c r="J48" s="3">
-        <v>20389300</v>
+        <v>20447600</v>
       </c>
       <c r="K48" s="3">
         <v>20130700</v>
@@ -4094,25 +4094,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2374000</v>
+        <v>2380800</v>
       </c>
       <c r="E49" s="3">
-        <v>2341400</v>
+        <v>2348100</v>
       </c>
       <c r="F49" s="3">
-        <v>2809100</v>
+        <v>2817100</v>
       </c>
       <c r="G49" s="3">
-        <v>2723400</v>
+        <v>2731100</v>
       </c>
       <c r="H49" s="3">
-        <v>2900200</v>
+        <v>2908500</v>
       </c>
       <c r="I49" s="3">
-        <v>2812300</v>
+        <v>2820400</v>
       </c>
       <c r="J49" s="3">
-        <v>2790600</v>
+        <v>2798600</v>
       </c>
       <c r="K49" s="3">
         <v>3426800</v>
@@ -4370,25 +4370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1514700</v>
+        <v>1519000</v>
       </c>
       <c r="E52" s="3">
-        <v>2861100</v>
+        <v>2869300</v>
       </c>
       <c r="F52" s="3">
-        <v>3410200</v>
+        <v>3419900</v>
       </c>
       <c r="G52" s="3">
-        <v>3189900</v>
+        <v>3199000</v>
       </c>
       <c r="H52" s="3">
-        <v>3300600</v>
+        <v>3310000</v>
       </c>
       <c r="I52" s="3">
-        <v>3140000</v>
+        <v>3149000</v>
       </c>
       <c r="J52" s="3">
-        <v>3205100</v>
+        <v>3214200</v>
       </c>
       <c r="K52" s="3">
         <v>3096200</v>
@@ -4554,25 +4554,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>54906400</v>
+        <v>55063300</v>
       </c>
       <c r="E54" s="3">
-        <v>54233700</v>
+        <v>54388700</v>
       </c>
       <c r="F54" s="3">
-        <v>59005600</v>
+        <v>59174100</v>
       </c>
       <c r="G54" s="3">
-        <v>61225500</v>
+        <v>61400400</v>
       </c>
       <c r="H54" s="3">
-        <v>68791200</v>
+        <v>68987700</v>
       </c>
       <c r="I54" s="3">
-        <v>65780300</v>
+        <v>65968200</v>
       </c>
       <c r="J54" s="3">
-        <v>63526800</v>
+        <v>63708300</v>
       </c>
       <c r="K54" s="3">
         <v>58322400</v>
@@ -4714,25 +4714,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4478900</v>
+        <v>4491700</v>
       </c>
       <c r="E57" s="3">
-        <v>4095900</v>
+        <v>4107600</v>
       </c>
       <c r="F57" s="3">
-        <v>4471300</v>
+        <v>4484100</v>
       </c>
       <c r="G57" s="3">
-        <v>5706000</v>
+        <v>5722300</v>
       </c>
       <c r="H57" s="3">
-        <v>6540400</v>
+        <v>6559100</v>
       </c>
       <c r="I57" s="3">
-        <v>5974000</v>
+        <v>5991100</v>
       </c>
       <c r="J57" s="3">
-        <v>6055400</v>
+        <v>6072700</v>
       </c>
       <c r="K57" s="3">
         <v>5268700</v>
@@ -4806,25 +4806,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1683900</v>
+        <v>1688700</v>
       </c>
       <c r="E58" s="3">
-        <v>1513600</v>
+        <v>1517900</v>
       </c>
       <c r="F58" s="3">
-        <v>1680700</v>
+        <v>1685500</v>
       </c>
       <c r="G58" s="3">
-        <v>1706700</v>
+        <v>1711600</v>
       </c>
       <c r="H58" s="3">
-        <v>1115400</v>
+        <v>1118600</v>
       </c>
       <c r="I58" s="3">
-        <v>2047400</v>
+        <v>2053200</v>
       </c>
       <c r="J58" s="3">
-        <v>1188100</v>
+        <v>1191500</v>
       </c>
       <c r="K58" s="3">
         <v>1383300</v>
@@ -4898,25 +4898,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5180900</v>
+        <v>5195700</v>
       </c>
       <c r="E59" s="3">
-        <v>4595000</v>
+        <v>4608100</v>
       </c>
       <c r="F59" s="3">
-        <v>6514300</v>
+        <v>6533000</v>
       </c>
       <c r="G59" s="3">
-        <v>7307500</v>
+        <v>7328400</v>
       </c>
       <c r="H59" s="3">
-        <v>11770100</v>
+        <v>11803700</v>
       </c>
       <c r="I59" s="3">
-        <v>10886900</v>
+        <v>10918000</v>
       </c>
       <c r="J59" s="3">
-        <v>11116900</v>
+        <v>11148700</v>
       </c>
       <c r="K59" s="3">
         <v>8175200</v>
@@ -4990,25 +4990,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11343700</v>
+        <v>11376100</v>
       </c>
       <c r="E60" s="3">
-        <v>10204400</v>
+        <v>10233600</v>
       </c>
       <c r="F60" s="3">
-        <v>12666300</v>
+        <v>12702500</v>
       </c>
       <c r="G60" s="3">
-        <v>14720200</v>
+        <v>14762300</v>
       </c>
       <c r="H60" s="3">
-        <v>19425800</v>
+        <v>19481300</v>
       </c>
       <c r="I60" s="3">
-        <v>18908300</v>
+        <v>18962300</v>
       </c>
       <c r="J60" s="3">
-        <v>18360400</v>
+        <v>18412800</v>
       </c>
       <c r="K60" s="3">
         <v>14827200</v>
@@ -5082,25 +5082,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8652900</v>
+        <v>8677600</v>
       </c>
       <c r="E61" s="3">
-        <v>8830800</v>
+        <v>8856000</v>
       </c>
       <c r="F61" s="3">
-        <v>9494800</v>
+        <v>9522000</v>
       </c>
       <c r="G61" s="3">
-        <v>9451400</v>
+        <v>9478400</v>
       </c>
       <c r="H61" s="3">
-        <v>10027600</v>
+        <v>10056200</v>
       </c>
       <c r="I61" s="3">
-        <v>10055800</v>
+        <v>10084500</v>
       </c>
       <c r="J61" s="3">
-        <v>10824000</v>
+        <v>10854900</v>
       </c>
       <c r="K61" s="3">
         <v>10382400</v>
@@ -5174,25 +5174,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7204400</v>
+        <v>7225000</v>
       </c>
       <c r="E62" s="3">
-        <v>8075700</v>
+        <v>8098700</v>
       </c>
       <c r="F62" s="3">
-        <v>7853200</v>
+        <v>7875700</v>
       </c>
       <c r="G62" s="3">
-        <v>8162500</v>
+        <v>8185800</v>
       </c>
       <c r="H62" s="3">
-        <v>9263700</v>
+        <v>9290200</v>
       </c>
       <c r="I62" s="3">
-        <v>8822100</v>
+        <v>8847300</v>
       </c>
       <c r="J62" s="3">
-        <v>9052200</v>
+        <v>9078000</v>
       </c>
       <c r="K62" s="3">
         <v>9266900</v>
@@ -5542,25 +5542,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>34927200</v>
+        <v>35027000</v>
       </c>
       <c r="E66" s="3">
-        <v>34925100</v>
+        <v>35024900</v>
       </c>
       <c r="F66" s="3">
-        <v>38196300</v>
+        <v>38305500</v>
       </c>
       <c r="G66" s="3">
-        <v>40447700</v>
+        <v>40563300</v>
       </c>
       <c r="H66" s="3">
-        <v>46900200</v>
+        <v>47034200</v>
       </c>
       <c r="I66" s="3">
-        <v>45557000</v>
+        <v>45687100</v>
       </c>
       <c r="J66" s="3">
-        <v>45477800</v>
+        <v>45607700</v>
       </c>
       <c r="K66" s="3">
         <v>41513400</v>
@@ -6036,25 +6036,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>16932500</v>
+        <v>16980900</v>
       </c>
       <c r="E72" s="3">
-        <v>16262000</v>
+        <v>16308400</v>
       </c>
       <c r="F72" s="3">
-        <v>17762500</v>
+        <v>17813300</v>
       </c>
       <c r="G72" s="3">
-        <v>18003400</v>
+        <v>18054800</v>
       </c>
       <c r="H72" s="3">
-        <v>18844300</v>
+        <v>18898100</v>
       </c>
       <c r="I72" s="3">
-        <v>17175600</v>
+        <v>17224600</v>
       </c>
       <c r="J72" s="3">
-        <v>15000100</v>
+        <v>15043000</v>
       </c>
       <c r="K72" s="3">
         <v>13671600</v>
@@ -6404,25 +6404,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19979200</v>
+        <v>20036300</v>
       </c>
       <c r="E76" s="3">
-        <v>19308700</v>
+        <v>19363800</v>
       </c>
       <c r="F76" s="3">
-        <v>20809200</v>
+        <v>20868700</v>
       </c>
       <c r="G76" s="3">
-        <v>20777800</v>
+        <v>20837100</v>
       </c>
       <c r="H76" s="3">
-        <v>21891000</v>
+        <v>21953500</v>
       </c>
       <c r="I76" s="3">
-        <v>20223300</v>
+        <v>20281100</v>
       </c>
       <c r="J76" s="3">
-        <v>18049000</v>
+        <v>18100500</v>
       </c>
       <c r="K76" s="3">
         <v>16809000</v>
@@ -6685,25 +6685,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>512100</v>
+        <v>513600</v>
       </c>
       <c r="E81" s="3">
-        <v>412300</v>
+        <v>413500</v>
       </c>
       <c r="F81" s="3">
-        <v>423200</v>
+        <v>424400</v>
       </c>
       <c r="G81" s="3">
-        <v>334200</v>
+        <v>335100</v>
       </c>
       <c r="H81" s="3">
-        <v>903800</v>
+        <v>906400</v>
       </c>
       <c r="I81" s="3">
-        <v>2112500</v>
+        <v>2118500</v>
       </c>
       <c r="J81" s="3">
-        <v>592400</v>
+        <v>594100</v>
       </c>
       <c r="K81" s="3">
         <v>583200</v>
@@ -6811,25 +6811,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>712800</v>
+        <v>714900</v>
       </c>
       <c r="E83" s="3">
-        <v>728000</v>
+        <v>730100</v>
       </c>
       <c r="F83" s="3">
-        <v>695500</v>
+        <v>697500</v>
       </c>
       <c r="G83" s="3">
-        <v>981900</v>
+        <v>984700</v>
       </c>
       <c r="H83" s="3">
-        <v>728000</v>
+        <v>730100</v>
       </c>
       <c r="I83" s="3">
-        <v>527300</v>
+        <v>528800</v>
       </c>
       <c r="J83" s="3">
-        <v>656400</v>
+        <v>658300</v>
       </c>
       <c r="K83" s="3">
         <v>2122700</v>
@@ -7363,25 +7363,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1849900</v>
+        <v>1855200</v>
       </c>
       <c r="E89" s="3">
-        <v>245200</v>
+        <v>245900</v>
       </c>
       <c r="F89" s="3">
-        <v>2914300</v>
+        <v>2922600</v>
       </c>
       <c r="G89" s="3">
-        <v>1560200</v>
+        <v>1564700</v>
       </c>
       <c r="H89" s="3">
-        <v>3452500</v>
+        <v>3462300</v>
       </c>
       <c r="I89" s="3">
-        <v>502400</v>
+        <v>503800</v>
       </c>
       <c r="J89" s="3">
-        <v>2902400</v>
+        <v>2910700</v>
       </c>
       <c r="K89" s="3">
         <v>3017100</v>
@@ -7765,25 +7765,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-272300</v>
+        <v>-273100</v>
       </c>
       <c r="E94" s="3">
-        <v>-853900</v>
+        <v>-856300</v>
       </c>
       <c r="F94" s="3">
-        <v>-1067600</v>
+        <v>-1070700</v>
       </c>
       <c r="G94" s="3">
-        <v>-1018800</v>
+        <v>-1021700</v>
       </c>
       <c r="H94" s="3">
-        <v>-971100</v>
+        <v>-973800</v>
       </c>
       <c r="I94" s="3">
-        <v>1112100</v>
+        <v>1115300</v>
       </c>
       <c r="J94" s="3">
-        <v>-1255300</v>
+        <v>-1258900</v>
       </c>
       <c r="K94" s="3">
         <v>-499800</v>
@@ -7891,19 +7891,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-39100</v>
+        <v>-39200</v>
       </c>
       <c r="E96" s="3">
-        <v>-2053900</v>
+        <v>-2059800</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>611900</v>
+        <v>613700</v>
       </c>
       <c r="H96" s="3">
-        <v>-304900</v>
+        <v>-305800</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -8259,25 +8259,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-120400</v>
+        <v>-120800</v>
       </c>
       <c r="E100" s="3">
-        <v>-2920800</v>
+        <v>-2929200</v>
       </c>
       <c r="F100" s="3">
-        <v>-115000</v>
+        <v>-115300</v>
       </c>
       <c r="G100" s="3">
-        <v>-13000</v>
+        <v>-13100</v>
       </c>
       <c r="H100" s="3">
-        <v>-1310700</v>
+        <v>-1314400</v>
       </c>
       <c r="I100" s="3">
-        <v>-1036200</v>
+        <v>-1039100</v>
       </c>
       <c r="J100" s="3">
-        <v>-526200</v>
+        <v>-527700</v>
       </c>
       <c r="K100" s="3">
         <v>-1433200</v>
@@ -8351,7 +8351,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="E101" s="3">
         <v>-7600</v>
@@ -8360,7 +8360,7 @@
         <v>-8700</v>
       </c>
       <c r="G101" s="3">
-        <v>-18400</v>
+        <v>-18500</v>
       </c>
       <c r="H101" s="3">
         <v>5400</v>
@@ -8369,7 +8369,7 @@
         <v>3300</v>
       </c>
       <c r="J101" s="3">
-        <v>-68400</v>
+        <v>-68600</v>
       </c>
       <c r="K101" s="3">
         <v>-10800</v>
@@ -8443,25 +8443,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1452800</v>
+        <v>1457000</v>
       </c>
       <c r="E102" s="3">
-        <v>-3537100</v>
+        <v>-3547200</v>
       </c>
       <c r="F102" s="3">
-        <v>1723000</v>
+        <v>1727900</v>
       </c>
       <c r="G102" s="3">
-        <v>510000</v>
+        <v>511400</v>
       </c>
       <c r="H102" s="3">
-        <v>1176100</v>
+        <v>1179500</v>
       </c>
       <c r="I102" s="3">
-        <v>581600</v>
+        <v>583200</v>
       </c>
       <c r="J102" s="3">
-        <v>1052500</v>
+        <v>1055500</v>
       </c>
       <c r="K102" s="3">
         <v>1073300</v>

--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10303200</v>
+        <v>8831500</v>
       </c>
       <c r="E8" s="3">
-        <v>9774400</v>
+        <v>10857800</v>
       </c>
       <c r="F8" s="3">
-        <v>11929900</v>
+        <v>10233100</v>
       </c>
       <c r="G8" s="3">
-        <v>15785100</v>
+        <v>9707900</v>
       </c>
       <c r="H8" s="3">
-        <v>18682700</v>
+        <v>11848800</v>
       </c>
       <c r="I8" s="3">
+        <v>15677700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>18555600</v>
+      </c>
+      <c r="K8" s="3">
         <v>16096300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>17222400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>14471700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9165500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>7687400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>6801900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4943100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3836100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3423300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5192700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7090800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>7287500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7099600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>6463100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>7854500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6210300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6265200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7141200</v>
+        <v>5976300</v>
       </c>
       <c r="E9" s="3">
-        <v>7097700</v>
+        <v>7656800</v>
       </c>
       <c r="F9" s="3">
-        <v>8764600</v>
+        <v>7092600</v>
       </c>
       <c r="G9" s="3">
-        <v>12165000</v>
+        <v>7049400</v>
       </c>
       <c r="H9" s="3">
-        <v>12923400</v>
+        <v>8705000</v>
       </c>
       <c r="I9" s="3">
+        <v>12082200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>12835500</v>
+      </c>
+      <c r="K9" s="3">
         <v>11628500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>10985500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>9568300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>6578800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>5091100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4397000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3634500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2510700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2211300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3708000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>4687200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4695400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>4537400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4302700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>5203600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>4239900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>4662100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3162000</v>
+        <v>2855200</v>
       </c>
       <c r="E10" s="3">
-        <v>2676700</v>
+        <v>3201000</v>
       </c>
       <c r="F10" s="3">
-        <v>3165300</v>
+        <v>3140500</v>
       </c>
       <c r="G10" s="3">
-        <v>3620100</v>
+        <v>2658500</v>
       </c>
       <c r="H10" s="3">
-        <v>5759300</v>
+        <v>3143800</v>
       </c>
       <c r="I10" s="3">
+        <v>3595500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5720100</v>
+      </c>
+      <c r="K10" s="3">
         <v>4467700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>6237000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4903400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2586700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2596300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2404800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1308600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1325400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1212000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1484700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2403700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2592100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2562200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2160300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2650900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1970400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1603100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>41300</v>
+        <v>18400</v>
       </c>
       <c r="E12" s="3">
-        <v>29400</v>
+        <v>122100</v>
       </c>
       <c r="F12" s="3">
-        <v>46800</v>
+        <v>41100</v>
       </c>
       <c r="G12" s="3">
-        <v>115300</v>
+        <v>29200</v>
       </c>
       <c r="H12" s="3">
-        <v>60900</v>
+        <v>46500</v>
       </c>
       <c r="I12" s="3">
+        <v>114600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>60500</v>
+      </c>
+      <c r="K12" s="3">
         <v>84900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>10900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>164800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>48500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>47600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>40200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>43900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>674600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>90500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>129800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>85200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>46500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>83500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>55000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>71000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>27700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>58200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>40600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>107700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>39300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>65100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>35900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>83300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,37 +1315,43 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-14100</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>76200</v>
+        <v>-14000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-14000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>75600</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>6500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-171900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1102200</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -1323,14 +1362,14 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>10</v>
@@ -1344,130 +1383,142 @@
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-158500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>165000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-68100</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>-153700</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>710500</v>
+        <v>670000</v>
       </c>
       <c r="E15" s="3">
-        <v>640900</v>
+        <v>612800</v>
       </c>
       <c r="F15" s="3">
-        <v>663700</v>
+        <v>705700</v>
       </c>
       <c r="G15" s="3">
-        <v>898800</v>
+        <v>636500</v>
       </c>
       <c r="H15" s="3">
-        <v>685500</v>
+        <v>659200</v>
       </c>
       <c r="I15" s="3">
+        <v>892700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>680800</v>
+      </c>
+      <c r="K15" s="3">
         <v>182800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>646300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2002300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>721500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>654900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>649600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>342100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>986000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>536700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>690500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>728500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>719100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>677600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>656700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>553600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>495100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>516100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>486400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>511600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>538600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>518400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>509400</v>
       </c>
-      <c r="AE15" s="3" t="s">
+      <c r="AG15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF15" s="3" t="s">
+      <c r="AH15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8920200</v>
+        <v>7598400</v>
       </c>
       <c r="E17" s="3">
-        <v>8568800</v>
+        <v>9527500</v>
       </c>
       <c r="F17" s="3">
-        <v>10525200</v>
+        <v>8859600</v>
       </c>
       <c r="G17" s="3">
-        <v>13887400</v>
+        <v>8510500</v>
       </c>
       <c r="H17" s="3">
-        <v>15026700</v>
+        <v>10453600</v>
       </c>
       <c r="I17" s="3">
+        <v>13793000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>14924500</v>
+      </c>
+      <c r="K17" s="3">
         <v>12480500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>15105000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>12857400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8184400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6549000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5756600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3494900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4510700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3330500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5054200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6229300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6264600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5986700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5652000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6430200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5483700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5738100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1383000</v>
+        <v>1233100</v>
       </c>
       <c r="E18" s="3">
-        <v>1205600</v>
+        <v>1330300</v>
       </c>
       <c r="F18" s="3">
-        <v>1404700</v>
+        <v>1373600</v>
       </c>
       <c r="G18" s="3">
-        <v>1897600</v>
+        <v>1197400</v>
       </c>
       <c r="H18" s="3">
-        <v>3656000</v>
+        <v>1395200</v>
       </c>
       <c r="I18" s="3">
+        <v>1884700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3631200</v>
+      </c>
+      <c r="K18" s="3">
         <v>3615800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2117400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1614200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>981100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1138400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1045300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1448200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-674600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>92700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>138500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>861500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1022900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1112900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>811000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1424200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>726600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>527000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>868500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>604800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>631700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1780,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>180600</v>
+        <v>214000</v>
       </c>
       <c r="E20" s="3">
-        <v>-194800</v>
+        <v>-57300</v>
       </c>
       <c r="F20" s="3">
-        <v>200200</v>
+        <v>179400</v>
       </c>
       <c r="G20" s="3">
-        <v>32600</v>
+        <v>-193400</v>
       </c>
       <c r="H20" s="3">
-        <v>62000</v>
+        <v>198800</v>
       </c>
       <c r="I20" s="3">
+        <v>32400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>61600</v>
+      </c>
+      <c r="K20" s="3">
         <v>489600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>293800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>139800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>218600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>219000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>212700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>84800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>57100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>52400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-51300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>131900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>144500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>227000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>161500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>88700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>154000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>176800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>90000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>25800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>225500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>113300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>149200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>118600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2278500</v>
+        <v>2118200</v>
       </c>
       <c r="E21" s="3">
-        <v>1741000</v>
+        <v>1975500</v>
       </c>
       <c r="F21" s="3">
-        <v>2302400</v>
+        <v>2263000</v>
       </c>
       <c r="G21" s="3">
-        <v>2915000</v>
+        <v>1729100</v>
       </c>
       <c r="H21" s="3">
-        <v>4448200</v>
+        <v>2286800</v>
       </c>
       <c r="I21" s="3">
+        <v>2895200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>4417900</v>
+      </c>
+      <c r="K21" s="3">
         <v>4634200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>3069500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3876700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1947000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2046200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1926600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2091500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>816800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>738500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>862900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1752300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1906100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2063400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1644800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2102000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1385600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1233100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>124000</v>
+        <v>104800</v>
       </c>
       <c r="E22" s="3">
-        <v>100100</v>
+        <v>114600</v>
       </c>
       <c r="F22" s="3">
-        <v>111000</v>
+        <v>123200</v>
       </c>
       <c r="G22" s="3">
-        <v>116400</v>
+        <v>99400</v>
       </c>
       <c r="H22" s="3">
-        <v>112100</v>
+        <v>110200</v>
       </c>
       <c r="I22" s="3">
+        <v>115600</v>
+      </c>
+      <c r="J22" s="3">
+        <v>111300</v>
+      </c>
+      <c r="K22" s="3">
         <v>120800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>103400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>90000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>105500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>80400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>81500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>70800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>73700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>68700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>81800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>85200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>95500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>90600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>89700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>82800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>77500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>94400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>70300</v>
       </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AC22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>80800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>69600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>68400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>74000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1439600</v>
+        <v>1342200</v>
       </c>
       <c r="E23" s="3">
-        <v>910700</v>
+        <v>1158500</v>
       </c>
       <c r="F23" s="3">
-        <v>1494000</v>
+        <v>1429800</v>
       </c>
       <c r="G23" s="3">
-        <v>1813900</v>
+        <v>904500</v>
       </c>
       <c r="H23" s="3">
-        <v>3606000</v>
+        <v>1483800</v>
       </c>
       <c r="I23" s="3">
+        <v>1801500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3581400</v>
+      </c>
+      <c r="K23" s="3">
         <v>3984600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2307900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1664100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1094100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1277000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1176500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1462200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-691200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>76400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>5500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>908200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1071900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1249300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>882800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1430100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>803000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>609400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>888300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>630600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>776400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>697500</v>
+        <v>618200</v>
       </c>
       <c r="E24" s="3">
-        <v>556000</v>
+        <v>814800</v>
       </c>
       <c r="F24" s="3">
-        <v>849800</v>
+        <v>692700</v>
       </c>
       <c r="G24" s="3">
-        <v>1327500</v>
+        <v>552200</v>
       </c>
       <c r="H24" s="3">
-        <v>2127200</v>
+        <v>844000</v>
       </c>
       <c r="I24" s="3">
+        <v>1318500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2112800</v>
+      </c>
+      <c r="K24" s="3">
         <v>1251300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1376400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>930200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>572900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>422100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>293100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-478800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-216900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>14200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>79600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>373600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>416500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>475300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>289500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>492100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>366600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>306300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>305200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>159300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>166100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>193000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>193000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>120900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>742100</v>
+        <v>724100</v>
       </c>
       <c r="E26" s="3">
-        <v>354700</v>
+        <v>343700</v>
       </c>
       <c r="F26" s="3">
-        <v>644200</v>
+        <v>737000</v>
       </c>
       <c r="G26" s="3">
-        <v>486400</v>
+        <v>352300</v>
       </c>
       <c r="H26" s="3">
-        <v>1478700</v>
+        <v>639800</v>
       </c>
       <c r="I26" s="3">
+        <v>483100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1468700</v>
+      </c>
+      <c r="K26" s="3">
         <v>2733300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>931400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>733900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>521200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>854900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>883400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1940900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-474300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>62200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-74200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>534700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>655400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>774100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>593300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>938000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>436400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>303000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>583000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>471200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>610400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>915500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>513600</v>
+        <v>505800</v>
       </c>
       <c r="E27" s="3">
-        <v>413500</v>
+        <v>255000</v>
       </c>
       <c r="F27" s="3">
-        <v>424400</v>
+        <v>510100</v>
       </c>
       <c r="G27" s="3">
-        <v>335100</v>
+        <v>410700</v>
       </c>
       <c r="H27" s="3">
-        <v>906400</v>
+        <v>421500</v>
       </c>
       <c r="I27" s="3">
+        <v>332900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>900200</v>
+      </c>
+      <c r="K27" s="3">
         <v>2118500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>594100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>583200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>300500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>658100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>691900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1875100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-505500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>26200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-173500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>414400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>520600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>638800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>423500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>719200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>244800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>222900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>445800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>348900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>491400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>798900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-180600</v>
+        <v>-214000</v>
       </c>
       <c r="E32" s="3">
-        <v>194800</v>
+        <v>57300</v>
       </c>
       <c r="F32" s="3">
-        <v>-200200</v>
+        <v>-179400</v>
       </c>
       <c r="G32" s="3">
-        <v>-32600</v>
+        <v>193400</v>
       </c>
       <c r="H32" s="3">
-        <v>-62000</v>
+        <v>-198800</v>
       </c>
       <c r="I32" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-489600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-293800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-139800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-218600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-219000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-212700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-84800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-57100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-52400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>51300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-131900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-144500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-227000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-161500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-88700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-154000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-176800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>513600</v>
+        <v>505800</v>
       </c>
       <c r="E33" s="3">
-        <v>413500</v>
+        <v>255000</v>
       </c>
       <c r="F33" s="3">
-        <v>424400</v>
+        <v>510100</v>
       </c>
       <c r="G33" s="3">
-        <v>335100</v>
+        <v>410700</v>
       </c>
       <c r="H33" s="3">
-        <v>906400</v>
+        <v>421500</v>
       </c>
       <c r="I33" s="3">
+        <v>332900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>900200</v>
+      </c>
+      <c r="K33" s="3">
         <v>2118500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>594100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>583200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>300500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>658100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>691900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1875100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-505500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>26200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-173500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>414400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>520600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>638800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>423500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>719200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>244800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>222900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>445800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>348900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>491400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>798900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>513600</v>
+        <v>505800</v>
       </c>
       <c r="E35" s="3">
-        <v>413500</v>
+        <v>255000</v>
       </c>
       <c r="F35" s="3">
-        <v>424400</v>
+        <v>510100</v>
       </c>
       <c r="G35" s="3">
-        <v>335100</v>
+        <v>410700</v>
       </c>
       <c r="H35" s="3">
-        <v>906400</v>
+        <v>421500</v>
       </c>
       <c r="I35" s="3">
+        <v>332900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>900200</v>
+      </c>
+      <c r="K35" s="3">
         <v>2118500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>594100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>583200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>300500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>658100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>691900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1875100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-505500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>26200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-173500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>414400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>520600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>638800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>423500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>719200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>244800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>222900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>445800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>348900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>491400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>798900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,836 +3523,892 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8469800</v>
+        <v>8465100</v>
       </c>
       <c r="E41" s="3">
-        <v>6806100</v>
+        <v>7478400</v>
       </c>
       <c r="F41" s="3">
-        <v>10293400</v>
+        <v>8412200</v>
       </c>
       <c r="G41" s="3">
-        <v>8802700</v>
+        <v>6759800</v>
       </c>
       <c r="H41" s="3">
-        <v>8278300</v>
+        <v>10223400</v>
       </c>
       <c r="I41" s="3">
+        <v>8742900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>8222000</v>
+      </c>
+      <c r="K41" s="3">
         <v>7118400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6550400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5474700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4373300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3271300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3625800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2846600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7608800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>6360000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3020700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3421700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3867300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4342100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4382900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4762400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3780200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3213800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2429700</v>
+        <v>1936600</v>
       </c>
       <c r="E42" s="3">
-        <v>2320900</v>
+        <v>2301900</v>
       </c>
       <c r="F42" s="3">
-        <v>2195800</v>
+        <v>2413200</v>
       </c>
       <c r="G42" s="3">
-        <v>4275100</v>
+        <v>2305100</v>
       </c>
       <c r="H42" s="3">
-        <v>8127000</v>
+        <v>2180900</v>
       </c>
       <c r="I42" s="3">
+        <v>4246100</v>
+      </c>
+      <c r="J42" s="3">
+        <v>8071700</v>
+      </c>
+      <c r="K42" s="3">
         <v>8400100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>8005200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>5580900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>6690800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9531500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3779200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3010200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3291200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>5491600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>6987300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>3643500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2736600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>3435100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>2978500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>3225800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>4229900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>2617600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>905400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>821300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3378600</v>
+        <v>3686300</v>
       </c>
       <c r="E43" s="3">
-        <v>3027100</v>
+        <v>3785700</v>
       </c>
       <c r="F43" s="3">
-        <v>4339300</v>
+        <v>3355600</v>
       </c>
       <c r="G43" s="3">
-        <v>4699500</v>
+        <v>3006500</v>
       </c>
       <c r="H43" s="3">
-        <v>6267500</v>
+        <v>4309800</v>
       </c>
       <c r="I43" s="3">
+        <v>4667500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>6224800</v>
+      </c>
+      <c r="K43" s="3">
         <v>5761500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5860500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5014000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3793900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4157900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4349400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3343300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1941900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1843600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2862500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3564100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3807300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3585700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4357800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4056200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3196500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2945900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4355700</v>
+        <v>4106700</v>
       </c>
       <c r="E44" s="3">
-        <v>4409000</v>
+        <v>3813800</v>
       </c>
       <c r="F44" s="3">
-        <v>4384000</v>
+        <v>4326000</v>
       </c>
       <c r="G44" s="3">
-        <v>5259900</v>
+        <v>4379000</v>
       </c>
       <c r="H44" s="3">
-        <v>5790900</v>
+        <v>4354100</v>
       </c>
       <c r="I44" s="3">
+        <v>5224100</v>
+      </c>
+      <c r="J44" s="3">
+        <v>5751500</v>
+      </c>
+      <c r="K44" s="3">
         <v>5589600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>4256600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3414900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3245800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2706400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2507500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2345900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1541300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1538200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1572000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2153900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2370400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1909300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2075400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1858300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1845300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1639300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1009800</v>
+        <v>1477300</v>
       </c>
       <c r="E45" s="3">
-        <v>943400</v>
+        <v>1458900</v>
       </c>
       <c r="F45" s="3">
-        <v>1040200</v>
+        <v>1002900</v>
       </c>
       <c r="G45" s="3">
-        <v>1302500</v>
+        <v>937000</v>
       </c>
       <c r="H45" s="3">
-        <v>1029300</v>
+        <v>1033100</v>
       </c>
       <c r="I45" s="3">
+        <v>1762600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1022300</v>
+      </c>
+      <c r="K45" s="3">
         <v>805200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>768200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>674300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>525500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>431700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>538500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>534600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>273000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>293500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>370900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>347900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>286600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>294100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>330200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>312300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>418700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>424900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>362300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>297300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>269300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>286100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>280500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>232400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19643500</v>
+        <v>19672000</v>
       </c>
       <c r="E46" s="3">
-        <v>17506400</v>
+        <v>18838800</v>
       </c>
       <c r="F46" s="3">
-        <v>22252700</v>
+        <v>19509900</v>
       </c>
       <c r="G46" s="3">
-        <v>24339700</v>
+        <v>17387400</v>
       </c>
       <c r="H46" s="3">
-        <v>29493000</v>
+        <v>22101400</v>
       </c>
       <c r="I46" s="3">
+        <v>24643200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>29292400</v>
+      </c>
+      <c r="K46" s="3">
         <v>27674700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>25440900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>20158800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>18629300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>20098800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>14800400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>12080500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>14656200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>15526900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>14813500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>13131000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>13068200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>13566200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>14124700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>14214900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>13470600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>10841700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9442500</v>
+        <v>8741800</v>
       </c>
       <c r="E47" s="3">
-        <v>9402300</v>
+        <v>9047600</v>
       </c>
       <c r="F47" s="3">
-        <v>9577500</v>
+        <v>9378300</v>
       </c>
       <c r="G47" s="3">
-        <v>10111700</v>
+        <v>9338300</v>
       </c>
       <c r="H47" s="3">
-        <v>12370600</v>
+        <v>9512300</v>
       </c>
       <c r="I47" s="3">
+        <v>10042900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>12286500</v>
+      </c>
+      <c r="K47" s="3">
         <v>11576300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>11807000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>11509900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>13968500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>13733900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>13026100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>11737400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>7767600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>8480700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>8646600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>8831500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>9770500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>6566700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6554000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>6707000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>5998800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>5680000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22077500</v>
+        <v>21594500</v>
       </c>
       <c r="E48" s="3">
-        <v>22262500</v>
+        <v>21701500</v>
       </c>
       <c r="F48" s="3">
-        <v>21107000</v>
+        <v>21927400</v>
       </c>
       <c r="G48" s="3">
-        <v>21018800</v>
+        <v>22111100</v>
       </c>
       <c r="H48" s="3">
-        <v>20905700</v>
+        <v>20963400</v>
       </c>
       <c r="I48" s="3">
+        <v>20875900</v>
+      </c>
+      <c r="J48" s="3">
+        <v>20763500</v>
+      </c>
+      <c r="K48" s="3">
         <v>20747900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20447600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>20130700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>19727700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>19286300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19232300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>19153100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>14920900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>16464000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>16726900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>19237700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>20358100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>19369400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>19616500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>17879500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>15679200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>15670700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2380800</v>
+        <v>2057700</v>
       </c>
       <c r="E49" s="3">
-        <v>2348100</v>
+        <v>1922600</v>
       </c>
       <c r="F49" s="3">
-        <v>2817100</v>
+        <v>2364600</v>
       </c>
       <c r="G49" s="3">
-        <v>2731100</v>
+        <v>2332200</v>
       </c>
       <c r="H49" s="3">
-        <v>2908500</v>
+        <v>2797900</v>
       </c>
       <c r="I49" s="3">
+        <v>2712600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2888700</v>
+      </c>
+      <c r="K49" s="3">
         <v>2820400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2798600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3426800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3611900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3541100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3695600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3434000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3190500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4212000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>4215300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4859900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>5203800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>4843200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>5048000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3923700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3202100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3188600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1519000</v>
+        <v>3331800</v>
       </c>
       <c r="E52" s="3">
-        <v>2869300</v>
+        <v>3241000</v>
       </c>
       <c r="F52" s="3">
-        <v>3419900</v>
+        <v>1508700</v>
       </c>
       <c r="G52" s="3">
-        <v>3199000</v>
+        <v>2849800</v>
       </c>
       <c r="H52" s="3">
-        <v>3310000</v>
+        <v>3396600</v>
       </c>
       <c r="I52" s="3">
+        <v>3177300</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3287500</v>
+      </c>
+      <c r="K52" s="3">
         <v>3149000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3214200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3096200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3285600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3253400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4170600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2737900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2099700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2086900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1795600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1074000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>977500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>905800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>958200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>996000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1256000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1408700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>935700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>55063300</v>
+        <v>55397800</v>
       </c>
       <c r="E54" s="3">
-        <v>54388700</v>
+        <v>54751500</v>
       </c>
       <c r="F54" s="3">
-        <v>59174100</v>
+        <v>54688800</v>
       </c>
       <c r="G54" s="3">
-        <v>61400400</v>
+        <v>54018800</v>
       </c>
       <c r="H54" s="3">
-        <v>68987700</v>
+        <v>58771700</v>
       </c>
       <c r="I54" s="3">
+        <v>61451800</v>
+      </c>
+      <c r="J54" s="3">
+        <v>68518500</v>
+      </c>
+      <c r="K54" s="3">
         <v>65968200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>63708300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>58322400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>59223000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>59913500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>54925000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>49142900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>42634900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>46770600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>46197900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>47134200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>49378100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>45251400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>46301300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>43721200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>39606700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>36789600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4967,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4491700</v>
+        <v>4089400</v>
       </c>
       <c r="E57" s="3">
-        <v>4107600</v>
+        <v>4274200</v>
       </c>
       <c r="F57" s="3">
-        <v>4484100</v>
+        <v>4461100</v>
       </c>
       <c r="G57" s="3">
-        <v>5722300</v>
+        <v>4079600</v>
       </c>
       <c r="H57" s="3">
-        <v>6559100</v>
+        <v>4453600</v>
       </c>
       <c r="I57" s="3">
+        <v>5683400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>6514500</v>
+      </c>
+      <c r="K57" s="3">
         <v>5991100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6072700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5268700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4034100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4424600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4777900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4292800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2667400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2607300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3769100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4850600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4789700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4173900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5197500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5205900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>4101400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3877000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1688700</v>
+        <v>1257900</v>
       </c>
       <c r="E58" s="3">
-        <v>1517900</v>
+        <v>1240600</v>
       </c>
       <c r="F58" s="3">
-        <v>1685500</v>
+        <v>1677200</v>
       </c>
       <c r="G58" s="3">
-        <v>1711600</v>
+        <v>1507600</v>
       </c>
       <c r="H58" s="3">
-        <v>1118600</v>
+        <v>1674000</v>
       </c>
       <c r="I58" s="3">
+        <v>1699900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1111000</v>
+      </c>
+      <c r="K58" s="3">
         <v>2053200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1191500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1383300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1852300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1045300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1936100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1689600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>855200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>916400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>613100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>943300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1768900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1664600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1934300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>997200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>965800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1001400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>274900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>218800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>190700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>305200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5195700</v>
+        <v>5214400</v>
       </c>
       <c r="E59" s="3">
-        <v>4608100</v>
+        <v>5125800</v>
       </c>
       <c r="F59" s="3">
-        <v>6533000</v>
+        <v>5160300</v>
       </c>
       <c r="G59" s="3">
-        <v>7328400</v>
+        <v>4576800</v>
       </c>
       <c r="H59" s="3">
-        <v>11803700</v>
+        <v>6488500</v>
       </c>
       <c r="I59" s="3">
+        <v>7747500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>11723400</v>
+      </c>
+      <c r="K59" s="3">
         <v>10918000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>11148700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>8175200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>10021600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11731100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5604200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4606000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5440700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6826900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>8336700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5174000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4881600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>5518500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5219000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5247300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>6182600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>4643400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11376100</v>
+        <v>10561700</v>
       </c>
       <c r="E60" s="3">
-        <v>10233600</v>
+        <v>10640600</v>
       </c>
       <c r="F60" s="3">
-        <v>12702500</v>
+        <v>11298700</v>
       </c>
       <c r="G60" s="3">
-        <v>14762300</v>
+        <v>10164000</v>
       </c>
       <c r="H60" s="3">
-        <v>19481300</v>
+        <v>12616100</v>
       </c>
       <c r="I60" s="3">
+        <v>15130900</v>
+      </c>
+      <c r="J60" s="3">
+        <v>19348900</v>
+      </c>
+      <c r="K60" s="3">
         <v>18962300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>18412800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14827200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>15908000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>17201000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>12318300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10588400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>8963300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>10350600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>12718900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>10967800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11440200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11357000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>12350800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11450500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>11249900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>9521900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8677600</v>
+        <v>8635900</v>
       </c>
       <c r="E61" s="3">
-        <v>8856000</v>
+        <v>8625100</v>
       </c>
       <c r="F61" s="3">
-        <v>9522000</v>
+        <v>8618600</v>
       </c>
       <c r="G61" s="3">
-        <v>9478400</v>
+        <v>8795800</v>
       </c>
       <c r="H61" s="3">
-        <v>10056200</v>
+        <v>9457200</v>
       </c>
       <c r="I61" s="3">
+        <v>9414000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>9987800</v>
+      </c>
+      <c r="K61" s="3">
         <v>10084500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10854900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10382400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>10311300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>10897400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>10944000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10215400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9427200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>9955600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6896700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7957100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>8107000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>6550200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>6260900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>5806900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>5052900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>5035400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7225000</v>
+        <v>7958300</v>
       </c>
       <c r="E62" s="3">
-        <v>8098700</v>
+        <v>8069600</v>
       </c>
       <c r="F62" s="3">
-        <v>7875700</v>
+        <v>7175800</v>
       </c>
       <c r="G62" s="3">
-        <v>8185800</v>
+        <v>8043700</v>
       </c>
       <c r="H62" s="3">
-        <v>9290200</v>
+        <v>7822100</v>
       </c>
       <c r="I62" s="3">
+        <v>8130100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>9227000</v>
+      </c>
+      <c r="K62" s="3">
         <v>8847300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>9078000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>9266900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>9469200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9649000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>9182400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>8491900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>7635800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8515600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>8213500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>8523300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>9412800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>8512400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>8335100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>8315800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>6928000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>6508900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>35027000</v>
+        <v>35073000</v>
       </c>
       <c r="E66" s="3">
-        <v>35024900</v>
+        <v>35041700</v>
       </c>
       <c r="F66" s="3">
-        <v>38305500</v>
+        <v>34788800</v>
       </c>
       <c r="G66" s="3">
-        <v>40563300</v>
+        <v>34786700</v>
       </c>
       <c r="H66" s="3">
-        <v>47034200</v>
+        <v>38045000</v>
       </c>
       <c r="I66" s="3">
+        <v>40756400</v>
+      </c>
+      <c r="J66" s="3">
+        <v>46714300</v>
+      </c>
+      <c r="K66" s="3">
         <v>45687100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>45607700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>41513400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>42509600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>44194800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>39133300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>35438600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>29841700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>32870200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>32113100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>31943800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>33628400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>30806400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>31501900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>29637600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>26852700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>24489800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>16980900</v>
+        <v>17289000</v>
       </c>
       <c r="E72" s="3">
-        <v>16308400</v>
+        <v>17674800</v>
       </c>
       <c r="F72" s="3">
-        <v>17813300</v>
+        <v>16865400</v>
       </c>
       <c r="G72" s="3">
-        <v>18054800</v>
+        <v>16197500</v>
       </c>
       <c r="H72" s="3">
-        <v>18898100</v>
+        <v>17692100</v>
       </c>
       <c r="I72" s="3">
+        <v>17932100</v>
+      </c>
+      <c r="J72" s="3">
+        <v>18769600</v>
+      </c>
+      <c r="K72" s="3">
         <v>17224600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>15043000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>13671600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>12888300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>11960700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>12032600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>10195400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>9106500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>11379300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>11564700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>12445800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>12920000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>11727500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>12038600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>11306200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>10196600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>9765600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>20036300</v>
+        <v>20324700</v>
       </c>
       <c r="E76" s="3">
-        <v>19363800</v>
+        <v>19709800</v>
       </c>
       <c r="F76" s="3">
-        <v>20868700</v>
+        <v>19900000</v>
       </c>
       <c r="G76" s="3">
-        <v>20837100</v>
+        <v>19232100</v>
       </c>
       <c r="H76" s="3">
-        <v>21953500</v>
+        <v>20726700</v>
       </c>
       <c r="I76" s="3">
+        <v>20695400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>21804200</v>
+      </c>
+      <c r="K76" s="3">
         <v>20281100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>18100500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>16809000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>16713500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15718700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15791700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13704300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>12793200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>13900400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>14084700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>15190300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>15749700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14445000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>14799400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14083600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>12754000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>12299800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>513600</v>
+        <v>505800</v>
       </c>
       <c r="E81" s="3">
-        <v>413500</v>
+        <v>255000</v>
       </c>
       <c r="F81" s="3">
-        <v>424400</v>
+        <v>510100</v>
       </c>
       <c r="G81" s="3">
-        <v>335100</v>
+        <v>410700</v>
       </c>
       <c r="H81" s="3">
-        <v>906400</v>
+        <v>421500</v>
       </c>
       <c r="I81" s="3">
+        <v>332900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>900200</v>
+      </c>
+      <c r="K81" s="3">
         <v>2118500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>594100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>583200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>300500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>658100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>691900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1875100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-505500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>26200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-173500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>414400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>520600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>638800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>423500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>719200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>244800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>222900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>445800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>348900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>491400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>798900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7200,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>714900</v>
+        <v>671100</v>
       </c>
       <c r="E83" s="3">
-        <v>730100</v>
+        <v>702500</v>
       </c>
       <c r="F83" s="3">
-        <v>697500</v>
+        <v>710000</v>
       </c>
       <c r="G83" s="3">
-        <v>984700</v>
+        <v>725100</v>
       </c>
       <c r="H83" s="3">
-        <v>730100</v>
+        <v>692700</v>
       </c>
       <c r="I83" s="3">
+        <v>978000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>725100</v>
+      </c>
+      <c r="K83" s="3">
         <v>528800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>658300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2122700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>747400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>688800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>668700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>558500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1434400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>593500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>775600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>758800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>738700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>723500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>672300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>589100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>505100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>529200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>494100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>596900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>548700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>584600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>500400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1855200</v>
+        <v>1970100</v>
       </c>
       <c r="E89" s="3">
-        <v>245900</v>
+        <v>1180100</v>
       </c>
       <c r="F89" s="3">
-        <v>2922600</v>
+        <v>1842600</v>
       </c>
       <c r="G89" s="3">
-        <v>1564700</v>
+        <v>244200</v>
       </c>
       <c r="H89" s="3">
-        <v>3462300</v>
+        <v>2902800</v>
       </c>
       <c r="I89" s="3">
+        <v>1554000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>3438800</v>
+      </c>
+      <c r="K89" s="3">
         <v>503800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2910700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3017100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1731700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1652600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1125700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>677200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>822000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>592400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1225100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1145200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1316900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1334000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1035900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1318900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1075500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1353800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>832500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>888600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>718400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7922,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-815000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-947000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-861000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-821000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-858000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-910000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-735000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-651000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-647000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-758000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-579000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-657000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-570300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-562500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-402700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-462500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-637100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-706300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-665200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-578800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-619600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-671900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-547200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-273100</v>
+        <v>-886200</v>
       </c>
       <c r="E94" s="3">
-        <v>-856300</v>
+        <v>-1086100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1070700</v>
+        <v>-271300</v>
       </c>
       <c r="G94" s="3">
-        <v>-1021700</v>
+        <v>-850500</v>
       </c>
       <c r="H94" s="3">
-        <v>-973800</v>
+        <v>-1063400</v>
       </c>
       <c r="I94" s="3">
+        <v>-1014800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-967200</v>
+      </c>
+      <c r="K94" s="3">
         <v>1115300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-499800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-641800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-118500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-688800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-440100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-472400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-699300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-744800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-488200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-886000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-495100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>379200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>445400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,100 +8350,108 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-39200</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-2059800</v>
+        <v>-436600</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-38900</v>
       </c>
       <c r="G96" s="3">
-        <v>613700</v>
+        <v>-2045800</v>
       </c>
       <c r="H96" s="3">
-        <v>-305800</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>609500</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-303700</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-91100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-35500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-451800</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-240000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>115600</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-908200</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>85200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-760900</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>59500</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8738,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-120800</v>
+        <v>-87500</v>
       </c>
       <c r="E100" s="3">
-        <v>-2929200</v>
+        <v>-931600</v>
       </c>
       <c r="F100" s="3">
-        <v>-115300</v>
+        <v>-120000</v>
       </c>
       <c r="G100" s="3">
-        <v>-13100</v>
+        <v>-2909200</v>
       </c>
       <c r="H100" s="3">
-        <v>-1314400</v>
+        <v>-114600</v>
       </c>
       <c r="I100" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1305500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-527700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-66800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>203100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-687200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1201900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>3212700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-661100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-640900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1214000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-818800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-275100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>288600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-39900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>886400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>191300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4400</v>
+        <v>1100</v>
       </c>
       <c r="E101" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="G101" s="3">
         <v>-7600</v>
       </c>
-      <c r="F101" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-18500</v>
-      </c>
       <c r="H101" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="J101" s="3">
         <v>5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>3300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-68600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-10800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-4300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-9500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-24900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-41500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-15200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-6100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>5900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-10800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>2400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1457000</v>
+        <v>997500</v>
       </c>
       <c r="E102" s="3">
-        <v>-3547200</v>
+        <v>-844000</v>
       </c>
       <c r="F102" s="3">
-        <v>1727900</v>
+        <v>1447100</v>
       </c>
       <c r="G102" s="3">
-        <v>511400</v>
+        <v>-3523100</v>
       </c>
       <c r="H102" s="3">
-        <v>1179500</v>
+        <v>1716200</v>
       </c>
       <c r="I102" s="3">
+        <v>507900</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1171500</v>
+      </c>
+      <c r="K102" s="3">
         <v>583200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1055500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1073300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1018700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-356500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>630600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1558900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3333800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-176700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-255700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-654100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>32900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-434200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>723900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>527200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>350300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>493700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>796600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>663200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>496500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8831500</v>
+        <v>9507600</v>
       </c>
       <c r="E8" s="3">
-        <v>10857800</v>
+        <v>9051300</v>
       </c>
       <c r="F8" s="3">
-        <v>10233100</v>
+        <v>11128100</v>
       </c>
       <c r="G8" s="3">
-        <v>9707900</v>
+        <v>10487900</v>
       </c>
       <c r="H8" s="3">
-        <v>11848800</v>
+        <v>9949600</v>
       </c>
       <c r="I8" s="3">
-        <v>15677700</v>
+        <v>12143700</v>
       </c>
       <c r="J8" s="3">
+        <v>16068000</v>
+      </c>
+      <c r="K8" s="3">
         <v>18555600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16096300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17222400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14471700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9165500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7687400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6801900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4943100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3836100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3423300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5192700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7090800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7287500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7099600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6463100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7854500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6210300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6265200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5976300</v>
+        <v>6532600</v>
       </c>
       <c r="E9" s="3">
-        <v>7656800</v>
+        <v>6125000</v>
       </c>
       <c r="F9" s="3">
-        <v>7092600</v>
+        <v>7847300</v>
       </c>
       <c r="G9" s="3">
-        <v>7049400</v>
+        <v>7269200</v>
       </c>
       <c r="H9" s="3">
-        <v>8705000</v>
+        <v>7224900</v>
       </c>
       <c r="I9" s="3">
-        <v>12082200</v>
+        <v>8921700</v>
       </c>
       <c r="J9" s="3">
+        <v>12383000</v>
+      </c>
+      <c r="K9" s="3">
         <v>12835500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11628500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10985500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9568300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6578800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5091100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4397000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3634500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2510700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2211300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3708000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4687200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4695400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4537400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4302700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5203600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4239900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4662100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2855200</v>
+        <v>2975000</v>
       </c>
       <c r="E10" s="3">
-        <v>3201000</v>
+        <v>2926300</v>
       </c>
       <c r="F10" s="3">
-        <v>3140500</v>
+        <v>3280700</v>
       </c>
       <c r="G10" s="3">
-        <v>2658500</v>
+        <v>3218700</v>
       </c>
       <c r="H10" s="3">
-        <v>3143800</v>
+        <v>2724700</v>
       </c>
       <c r="I10" s="3">
-        <v>3595500</v>
+        <v>3222000</v>
       </c>
       <c r="J10" s="3">
+        <v>3685000</v>
+      </c>
+      <c r="K10" s="3">
         <v>5720100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4467700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6237000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4903400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2586700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2596300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2404800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1308600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1325400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1212000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1484700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2403700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2592100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2562200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2160300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2650900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1970400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1603100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>18400</v>
+        <v>26600</v>
       </c>
       <c r="E12" s="3">
-        <v>122100</v>
+        <v>18800</v>
       </c>
       <c r="F12" s="3">
-        <v>41100</v>
+        <v>125200</v>
       </c>
       <c r="G12" s="3">
-        <v>29200</v>
+        <v>42100</v>
       </c>
       <c r="H12" s="3">
+        <v>29900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>47600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>117400</v>
+      </c>
+      <c r="K12" s="3">
+        <v>60500</v>
+      </c>
+      <c r="L12" s="3">
+        <v>84900</v>
+      </c>
+      <c r="M12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="N12" s="3">
+        <v>164800</v>
+      </c>
+      <c r="O12" s="3">
+        <v>48500</v>
+      </c>
+      <c r="P12" s="3">
+        <v>47600</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>40200</v>
+      </c>
+      <c r="R12" s="3">
+        <v>43900</v>
+      </c>
+      <c r="S12" s="3">
+        <v>674600</v>
+      </c>
+      <c r="T12" s="3">
+        <v>90500</v>
+      </c>
+      <c r="U12" s="3">
+        <v>129800</v>
+      </c>
+      <c r="V12" s="3">
+        <v>85200</v>
+      </c>
+      <c r="W12" s="3">
         <v>46500</v>
       </c>
-      <c r="I12" s="3">
-        <v>114600</v>
-      </c>
-      <c r="J12" s="3">
-        <v>60500</v>
-      </c>
-      <c r="K12" s="3">
-        <v>84900</v>
-      </c>
-      <c r="L12" s="3">
-        <v>10900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>164800</v>
-      </c>
-      <c r="N12" s="3">
-        <v>48500</v>
-      </c>
-      <c r="O12" s="3">
-        <v>47600</v>
-      </c>
-      <c r="P12" s="3">
-        <v>40200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>43900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>674600</v>
-      </c>
-      <c r="S12" s="3">
-        <v>90500</v>
-      </c>
-      <c r="T12" s="3">
-        <v>129800</v>
-      </c>
-      <c r="U12" s="3">
-        <v>85200</v>
-      </c>
-      <c r="V12" s="3">
-        <v>46500</v>
-      </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>83500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>55000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>71000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>27700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>58200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>40600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>107700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>39300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>65100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>35900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>83300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,40 +1338,43 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>136200</v>
       </c>
       <c r="E14" s="3">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-14000</v>
+        <v>-14400</v>
       </c>
       <c r="G14" s="3">
-        <v>75600</v>
+        <v>-14400</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>77500</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>6500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-171900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1102200</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
@@ -1368,11 +1388,11 @@
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
@@ -1389,136 +1409,142 @@
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-158500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>165000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-68100</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-153700</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>670000</v>
+        <v>686700</v>
       </c>
       <c r="E15" s="3">
-        <v>612800</v>
+        <v>686700</v>
       </c>
       <c r="F15" s="3">
-        <v>705700</v>
+        <v>628000</v>
       </c>
       <c r="G15" s="3">
-        <v>636500</v>
+        <v>723300</v>
       </c>
       <c r="H15" s="3">
-        <v>659200</v>
+        <v>652400</v>
       </c>
       <c r="I15" s="3">
-        <v>892700</v>
+        <v>675600</v>
       </c>
       <c r="J15" s="3">
+        <v>914900</v>
+      </c>
+      <c r="K15" s="3">
         <v>680800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>182800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>646300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2002300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>721500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>654900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>649600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>342100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>986000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>536700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>690500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>728500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>719100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>677600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>656700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>553600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>495100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>516100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>486400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>511600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>538600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>518400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>509400</v>
-      </c>
-      <c r="AG15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7598400</v>
+        <v>8362400</v>
       </c>
       <c r="E17" s="3">
-        <v>9527500</v>
+        <v>7787500</v>
       </c>
       <c r="F17" s="3">
-        <v>8859600</v>
+        <v>9764600</v>
       </c>
       <c r="G17" s="3">
-        <v>8510500</v>
+        <v>9080100</v>
       </c>
       <c r="H17" s="3">
-        <v>10453600</v>
+        <v>8722400</v>
       </c>
       <c r="I17" s="3">
-        <v>13793000</v>
+        <v>10713800</v>
       </c>
       <c r="J17" s="3">
+        <v>14136300</v>
+      </c>
+      <c r="K17" s="3">
         <v>14924500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12480500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15105000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12857400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8184400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6549000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5756600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3494900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4510700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3330500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5054200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6229300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6264600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5986700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5652000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6430200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5483700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5738100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1233100</v>
+        <v>1145300</v>
       </c>
       <c r="E18" s="3">
-        <v>1330300</v>
+        <v>1263800</v>
       </c>
       <c r="F18" s="3">
-        <v>1373600</v>
+        <v>1363500</v>
       </c>
       <c r="G18" s="3">
-        <v>1197400</v>
+        <v>1407800</v>
       </c>
       <c r="H18" s="3">
-        <v>1395200</v>
+        <v>1227200</v>
       </c>
       <c r="I18" s="3">
-        <v>1884700</v>
+        <v>1429900</v>
       </c>
       <c r="J18" s="3">
+        <v>1931700</v>
+      </c>
+      <c r="K18" s="3">
         <v>3631200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3615800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2117400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1614200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>981100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1138400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1045300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1448200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-674600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>92700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>138500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>861500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1022900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1112900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>811000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1424200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>726600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>527000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>868500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>604800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>631700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>214000</v>
+        <v>186100</v>
       </c>
       <c r="E20" s="3">
-        <v>-57300</v>
+        <v>219300</v>
       </c>
       <c r="F20" s="3">
-        <v>179400</v>
+        <v>-58700</v>
       </c>
       <c r="G20" s="3">
-        <v>-193400</v>
+        <v>183900</v>
       </c>
       <c r="H20" s="3">
-        <v>198800</v>
+        <v>-198300</v>
       </c>
       <c r="I20" s="3">
-        <v>32400</v>
+        <v>203800</v>
       </c>
       <c r="J20" s="3">
+        <v>33200</v>
+      </c>
+      <c r="K20" s="3">
         <v>61600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>489600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>293800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>139800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>218600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>219000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>212700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>84800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>57100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>52400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-51300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>131900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>144500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>227000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>161500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>88700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>154000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>176800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>90000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>25800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>225500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>113300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>149200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>118600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2118200</v>
+        <v>2160900</v>
       </c>
       <c r="E21" s="3">
-        <v>1975500</v>
+        <v>2170900</v>
       </c>
       <c r="F21" s="3">
-        <v>2263000</v>
+        <v>2024700</v>
       </c>
       <c r="G21" s="3">
-        <v>1729100</v>
+        <v>2319300</v>
       </c>
       <c r="H21" s="3">
-        <v>2286800</v>
+        <v>1772200</v>
       </c>
       <c r="I21" s="3">
-        <v>2895200</v>
+        <v>2343700</v>
       </c>
       <c r="J21" s="3">
+        <v>2967300</v>
+      </c>
+      <c r="K21" s="3">
         <v>4417900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4634200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3069500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3876700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1947000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2046200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1926600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2091500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>816800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>738500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>862900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1752300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1906100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2063400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1644800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2102000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1385600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1233100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>104800</v>
+        <v>113000</v>
       </c>
       <c r="E22" s="3">
-        <v>114600</v>
+        <v>107400</v>
       </c>
       <c r="F22" s="3">
-        <v>123200</v>
+        <v>117400</v>
       </c>
       <c r="G22" s="3">
-        <v>99400</v>
+        <v>126300</v>
       </c>
       <c r="H22" s="3">
-        <v>110200</v>
+        <v>101900</v>
       </c>
       <c r="I22" s="3">
-        <v>115600</v>
+        <v>113000</v>
       </c>
       <c r="J22" s="3">
+        <v>118500</v>
+      </c>
+      <c r="K22" s="3">
         <v>111300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>120800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>103400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>90000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>105500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>80400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>81500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>70800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>73700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>68700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>81800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>85200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>95500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>90600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>89700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>82800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>77500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>94400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>70300</v>
       </c>
-      <c r="AC22" s="3" t="s">
+      <c r="AD22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>80800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>69600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>68400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>74000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1342200</v>
+        <v>1218400</v>
       </c>
       <c r="E23" s="3">
-        <v>1158500</v>
+        <v>1375600</v>
       </c>
       <c r="F23" s="3">
-        <v>1429800</v>
+        <v>1187300</v>
       </c>
       <c r="G23" s="3">
-        <v>904500</v>
+        <v>1465400</v>
       </c>
       <c r="H23" s="3">
-        <v>1483800</v>
+        <v>927100</v>
       </c>
       <c r="I23" s="3">
-        <v>1801500</v>
+        <v>1520700</v>
       </c>
       <c r="J23" s="3">
+        <v>1846400</v>
+      </c>
+      <c r="K23" s="3">
         <v>3581400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3984600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2307900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1664100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1094100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1277000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1176500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1462200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-691200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>76400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>908200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1071900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1249300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>882800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1430100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>803000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>609400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>888300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>630600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>776400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>618200</v>
+        <v>608100</v>
       </c>
       <c r="E24" s="3">
-        <v>814800</v>
+        <v>633500</v>
       </c>
       <c r="F24" s="3">
-        <v>692700</v>
+        <v>835100</v>
       </c>
       <c r="G24" s="3">
-        <v>552200</v>
+        <v>710000</v>
       </c>
       <c r="H24" s="3">
-        <v>844000</v>
+        <v>566000</v>
       </c>
       <c r="I24" s="3">
-        <v>1318500</v>
+        <v>865000</v>
       </c>
       <c r="J24" s="3">
+        <v>1351300</v>
+      </c>
+      <c r="K24" s="3">
         <v>2112800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1251300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1376400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>930200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>572900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>422100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>293100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-478800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-216900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>79600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>373600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>416500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>475300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>289500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>492100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>366600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>306300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>305200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>159300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>166100</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>193000</v>
       </c>
       <c r="AF24" s="3">
         <v>193000</v>
       </c>
       <c r="AG24" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AH24" s="3">
         <v>120900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>724100</v>
+        <v>610300</v>
       </c>
       <c r="E26" s="3">
-        <v>343700</v>
+        <v>742100</v>
       </c>
       <c r="F26" s="3">
-        <v>737000</v>
+        <v>352200</v>
       </c>
       <c r="G26" s="3">
-        <v>352300</v>
+        <v>755400</v>
       </c>
       <c r="H26" s="3">
-        <v>639800</v>
+        <v>361100</v>
       </c>
       <c r="I26" s="3">
-        <v>483100</v>
+        <v>655700</v>
       </c>
       <c r="J26" s="3">
+        <v>495100</v>
+      </c>
+      <c r="K26" s="3">
         <v>1468700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2733300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>931400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>733900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>521200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>854900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>883400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1940900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-474300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>62200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-74200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>534700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>655400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>774100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>593300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>938000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>436400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>303000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>583000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>471200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>610400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>915500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>505800</v>
+        <v>418700</v>
       </c>
       <c r="E27" s="3">
-        <v>255000</v>
+        <v>518400</v>
       </c>
       <c r="F27" s="3">
-        <v>510100</v>
+        <v>261400</v>
       </c>
       <c r="G27" s="3">
-        <v>410700</v>
+        <v>522800</v>
       </c>
       <c r="H27" s="3">
-        <v>421500</v>
+        <v>420900</v>
       </c>
       <c r="I27" s="3">
-        <v>332900</v>
+        <v>432000</v>
       </c>
       <c r="J27" s="3">
+        <v>341100</v>
+      </c>
+      <c r="K27" s="3">
         <v>900200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2118500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>594100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>583200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>658100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>691900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1875100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-505500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>26200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-173500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>414400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>520600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>638800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>423500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>719200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>244800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>222900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>445800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>348900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>491400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>798900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-214000</v>
+        <v>-186100</v>
       </c>
       <c r="E32" s="3">
-        <v>57300</v>
+        <v>-219300</v>
       </c>
       <c r="F32" s="3">
-        <v>-179400</v>
+        <v>58700</v>
       </c>
       <c r="G32" s="3">
-        <v>193400</v>
+        <v>-183900</v>
       </c>
       <c r="H32" s="3">
-        <v>-198800</v>
+        <v>198300</v>
       </c>
       <c r="I32" s="3">
-        <v>-32400</v>
+        <v>-203800</v>
       </c>
       <c r="J32" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-61600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-489600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-293800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-139800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-218600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-219000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-212700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-84800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-57100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-52400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>51300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-131900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-144500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-227000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-161500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-88700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>505800</v>
+        <v>418700</v>
       </c>
       <c r="E33" s="3">
-        <v>255000</v>
+        <v>518400</v>
       </c>
       <c r="F33" s="3">
-        <v>510100</v>
+        <v>261400</v>
       </c>
       <c r="G33" s="3">
-        <v>410700</v>
+        <v>522800</v>
       </c>
       <c r="H33" s="3">
-        <v>421500</v>
+        <v>420900</v>
       </c>
       <c r="I33" s="3">
-        <v>332900</v>
+        <v>432000</v>
       </c>
       <c r="J33" s="3">
+        <v>341100</v>
+      </c>
+      <c r="K33" s="3">
         <v>900200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2118500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>594100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>583200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>300500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>658100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>691900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1875100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-505500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>26200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-173500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>414400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>520600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>638800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>423500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>719200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>244800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>222900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>445800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>348900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>491400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>798900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>505800</v>
+        <v>418700</v>
       </c>
       <c r="E35" s="3">
-        <v>255000</v>
+        <v>518400</v>
       </c>
       <c r="F35" s="3">
-        <v>510100</v>
+        <v>261400</v>
       </c>
       <c r="G35" s="3">
-        <v>410700</v>
+        <v>522800</v>
       </c>
       <c r="H35" s="3">
-        <v>421500</v>
+        <v>420900</v>
       </c>
       <c r="I35" s="3">
-        <v>332900</v>
+        <v>432000</v>
       </c>
       <c r="J35" s="3">
+        <v>341100</v>
+      </c>
+      <c r="K35" s="3">
         <v>900200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2118500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>594100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>583200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>300500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>658100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>691900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1875100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-505500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>26200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-173500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>414400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>520600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>638800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>423500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>719200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>244800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>222900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>445800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>348900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>491400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>798900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,890 +3611,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8465100</v>
+        <v>5864700</v>
       </c>
       <c r="E41" s="3">
-        <v>7478400</v>
+        <v>8675800</v>
       </c>
       <c r="F41" s="3">
-        <v>8412200</v>
+        <v>7664600</v>
       </c>
       <c r="G41" s="3">
-        <v>6759800</v>
+        <v>8621600</v>
       </c>
       <c r="H41" s="3">
-        <v>10223400</v>
+        <v>6928000</v>
       </c>
       <c r="I41" s="3">
-        <v>8742900</v>
+        <v>10477900</v>
       </c>
       <c r="J41" s="3">
+        <v>8960500</v>
+      </c>
+      <c r="K41" s="3">
         <v>8222000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7118400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6550400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5474700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4373300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3271300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3625800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2846600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7608800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6360000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3020700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3421700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3867300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4342100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4382900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4762400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3780200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3213800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1936600</v>
+        <v>1520700</v>
       </c>
       <c r="E42" s="3">
-        <v>2301900</v>
+        <v>1984800</v>
       </c>
       <c r="F42" s="3">
-        <v>2413200</v>
+        <v>2359200</v>
       </c>
       <c r="G42" s="3">
-        <v>2305100</v>
+        <v>2473300</v>
       </c>
       <c r="H42" s="3">
-        <v>2180900</v>
+        <v>2362500</v>
       </c>
       <c r="I42" s="3">
-        <v>4246100</v>
+        <v>2235100</v>
       </c>
       <c r="J42" s="3">
+        <v>4351800</v>
+      </c>
+      <c r="K42" s="3">
         <v>8071700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8400100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8005200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5580900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6690800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9531500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3779200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3010200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3291200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5491600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6987300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3643500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2736600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3435100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2978500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3225800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4229900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2617600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>905400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>821300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3686300</v>
+        <v>3287400</v>
       </c>
       <c r="E43" s="3">
-        <v>3785700</v>
+        <v>3778000</v>
       </c>
       <c r="F43" s="3">
-        <v>3355600</v>
+        <v>3879900</v>
       </c>
       <c r="G43" s="3">
-        <v>3006500</v>
+        <v>3439100</v>
       </c>
       <c r="H43" s="3">
-        <v>4309800</v>
+        <v>3081300</v>
       </c>
       <c r="I43" s="3">
-        <v>4667500</v>
+        <v>4417100</v>
       </c>
       <c r="J43" s="3">
+        <v>4783700</v>
+      </c>
+      <c r="K43" s="3">
         <v>6224800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5761500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5860500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5014000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3793900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4157900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4349400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3343300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1941900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1843600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2862500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3564100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3807300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3585700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4357800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4056200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3196500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2945900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4106700</v>
+        <v>4242100</v>
       </c>
       <c r="E44" s="3">
-        <v>3813800</v>
+        <v>4208900</v>
       </c>
       <c r="F44" s="3">
-        <v>4326000</v>
+        <v>3908700</v>
       </c>
       <c r="G44" s="3">
-        <v>4379000</v>
+        <v>4433700</v>
       </c>
       <c r="H44" s="3">
-        <v>4354100</v>
+        <v>4488000</v>
       </c>
       <c r="I44" s="3">
-        <v>5224100</v>
+        <v>4462500</v>
       </c>
       <c r="J44" s="3">
+        <v>5354100</v>
+      </c>
+      <c r="K44" s="3">
         <v>5751500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5589600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4256600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3414900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3245800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2706400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2507500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2345900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1541300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1538200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1572000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2153900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2370400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1909300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2075400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1858300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1845300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1639300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1477300</v>
+        <v>1156300</v>
       </c>
       <c r="E45" s="3">
-        <v>1458900</v>
+        <v>1514100</v>
       </c>
       <c r="F45" s="3">
-        <v>1002900</v>
+        <v>1495300</v>
       </c>
       <c r="G45" s="3">
-        <v>937000</v>
+        <v>1027900</v>
       </c>
       <c r="H45" s="3">
-        <v>1033100</v>
+        <v>960300</v>
       </c>
       <c r="I45" s="3">
-        <v>1762600</v>
+        <v>1058900</v>
       </c>
       <c r="J45" s="3">
+        <v>1806500</v>
+      </c>
+      <c r="K45" s="3">
         <v>1022300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>805200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>768200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>674300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>525500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>431700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>538500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>534600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>273000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>293500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>370900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>347900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>286600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>294100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>330200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>312300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>418700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>424900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>362300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>297300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>269300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>286100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>280500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>232400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19672000</v>
+        <v>16071300</v>
       </c>
       <c r="E46" s="3">
-        <v>18838800</v>
+        <v>20161600</v>
       </c>
       <c r="F46" s="3">
-        <v>19509900</v>
+        <v>19307700</v>
       </c>
       <c r="G46" s="3">
-        <v>17387400</v>
+        <v>19995500</v>
       </c>
       <c r="H46" s="3">
-        <v>22101400</v>
+        <v>17820200</v>
       </c>
       <c r="I46" s="3">
-        <v>24643200</v>
+        <v>22651500</v>
       </c>
       <c r="J46" s="3">
+        <v>25256600</v>
+      </c>
+      <c r="K46" s="3">
         <v>29292400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27674700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25440900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20158800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18629300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20098800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14800400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12080500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14656200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15526900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14813500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13131000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13068200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13566200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14124700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14214900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13470600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10841700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8741800</v>
+        <v>9234100</v>
       </c>
       <c r="E47" s="3">
-        <v>9047600</v>
+        <v>8959400</v>
       </c>
       <c r="F47" s="3">
-        <v>9378300</v>
+        <v>9272800</v>
       </c>
       <c r="G47" s="3">
-        <v>9338300</v>
+        <v>9611800</v>
       </c>
       <c r="H47" s="3">
-        <v>9512300</v>
+        <v>9570800</v>
       </c>
       <c r="I47" s="3">
-        <v>10042900</v>
+        <v>9749100</v>
       </c>
       <c r="J47" s="3">
+        <v>10292900</v>
+      </c>
+      <c r="K47" s="3">
         <v>12286500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11576300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11807000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11509900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13968500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13733900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13026100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11737400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7767600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8480700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8646600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8831500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9770500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6566700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6554000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6707000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5998800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5680000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21594500</v>
+        <v>22025700</v>
       </c>
       <c r="E48" s="3">
-        <v>21701500</v>
+        <v>22132100</v>
       </c>
       <c r="F48" s="3">
-        <v>21927400</v>
+        <v>22241700</v>
       </c>
       <c r="G48" s="3">
-        <v>22111100</v>
+        <v>22473200</v>
       </c>
       <c r="H48" s="3">
-        <v>20963400</v>
+        <v>22661500</v>
       </c>
       <c r="I48" s="3">
-        <v>20875900</v>
+        <v>21485200</v>
       </c>
       <c r="J48" s="3">
+        <v>21395500</v>
+      </c>
+      <c r="K48" s="3">
         <v>20763500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20747900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20447600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20130700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19727700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19286300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19232300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19153100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14920900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16464000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16726900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19237700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20358100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19369400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19616500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>17879500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>15679200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>15670700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2057700</v>
+        <v>2143200</v>
       </c>
       <c r="E49" s="3">
-        <v>1922600</v>
+        <v>2108900</v>
       </c>
       <c r="F49" s="3">
-        <v>2364600</v>
+        <v>1970400</v>
       </c>
       <c r="G49" s="3">
-        <v>2332200</v>
+        <v>2423400</v>
       </c>
       <c r="H49" s="3">
-        <v>2797900</v>
+        <v>2390200</v>
       </c>
       <c r="I49" s="3">
-        <v>2712600</v>
+        <v>2867600</v>
       </c>
       <c r="J49" s="3">
+        <v>2780100</v>
+      </c>
+      <c r="K49" s="3">
         <v>2888700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2820400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2798600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3426800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3611900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3541100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3695600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3434000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3190500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4212000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4215300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4859900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5203800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4843200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5048000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3923700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3202100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3188600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3331800</v>
+        <v>3677200</v>
       </c>
       <c r="E52" s="3">
-        <v>3241000</v>
+        <v>3414700</v>
       </c>
       <c r="F52" s="3">
-        <v>1508700</v>
+        <v>3321700</v>
       </c>
       <c r="G52" s="3">
-        <v>2849800</v>
+        <v>1546200</v>
       </c>
       <c r="H52" s="3">
-        <v>3396600</v>
+        <v>2920700</v>
       </c>
       <c r="I52" s="3">
-        <v>3177300</v>
+        <v>3481200</v>
       </c>
       <c r="J52" s="3">
+        <v>3256300</v>
+      </c>
+      <c r="K52" s="3">
         <v>3287500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3149000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3214200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3096200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3285600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3253400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4170600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2737900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2099700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2086900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1795600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1074000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>977500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>905800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>958200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>996000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1256000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1408700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>935700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>55397800</v>
+        <v>53151500</v>
       </c>
       <c r="E54" s="3">
-        <v>54751500</v>
+        <v>56776700</v>
       </c>
       <c r="F54" s="3">
-        <v>54688800</v>
+        <v>56114300</v>
       </c>
       <c r="G54" s="3">
-        <v>54018800</v>
+        <v>56050100</v>
       </c>
       <c r="H54" s="3">
-        <v>58771700</v>
+        <v>55363400</v>
       </c>
       <c r="I54" s="3">
-        <v>61451800</v>
+        <v>60234600</v>
       </c>
       <c r="J54" s="3">
+        <v>62981500</v>
+      </c>
+      <c r="K54" s="3">
         <v>68518500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65968200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>63708300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58322400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>59223000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>59913500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54925000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>49142900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42634900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46770600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>46197900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47134200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49378100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>45251400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>46301300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>43721200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39606700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>36789600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4089400</v>
+        <v>3961900</v>
       </c>
       <c r="E57" s="3">
-        <v>4274200</v>
+        <v>4191200</v>
       </c>
       <c r="F57" s="3">
-        <v>4461100</v>
+        <v>4380600</v>
       </c>
       <c r="G57" s="3">
-        <v>4079600</v>
+        <v>4572200</v>
       </c>
       <c r="H57" s="3">
-        <v>4453600</v>
+        <v>4181200</v>
       </c>
       <c r="I57" s="3">
-        <v>5683400</v>
+        <v>4564400</v>
       </c>
       <c r="J57" s="3">
+        <v>5824900</v>
+      </c>
+      <c r="K57" s="3">
         <v>6514500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5991100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6072700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5268700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4034100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4424600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4777900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4292800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2667400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2607300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3769100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4850600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4789700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4173900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5197500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5205900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4101400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3877000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1257900</v>
+        <v>1134200</v>
       </c>
       <c r="E58" s="3">
-        <v>1240600</v>
+        <v>1289200</v>
       </c>
       <c r="F58" s="3">
-        <v>1677200</v>
+        <v>1271500</v>
       </c>
       <c r="G58" s="3">
-        <v>1507600</v>
+        <v>1719000</v>
       </c>
       <c r="H58" s="3">
-        <v>1674000</v>
+        <v>1545100</v>
       </c>
       <c r="I58" s="3">
-        <v>1699900</v>
+        <v>1715700</v>
       </c>
       <c r="J58" s="3">
+        <v>1742300</v>
+      </c>
+      <c r="K58" s="3">
         <v>1111000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2053200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1191500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1383300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1852300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1045300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1936100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1689600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>855200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>916400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>613100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>943300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1768900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1664600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1934300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>997200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>965800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1001400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>274900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>218800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>190700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>305200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5214400</v>
+        <v>4378300</v>
       </c>
       <c r="E59" s="3">
-        <v>5125800</v>
+        <v>5344200</v>
       </c>
       <c r="F59" s="3">
-        <v>5160300</v>
+        <v>5253300</v>
       </c>
       <c r="G59" s="3">
-        <v>4576800</v>
+        <v>5288800</v>
       </c>
       <c r="H59" s="3">
-        <v>6488500</v>
+        <v>4690700</v>
       </c>
       <c r="I59" s="3">
-        <v>7747500</v>
+        <v>6650000</v>
       </c>
       <c r="J59" s="3">
+        <v>7940400</v>
+      </c>
+      <c r="K59" s="3">
         <v>11723400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10918000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11148700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8175200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10021600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11731100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5604200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4606000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5440700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6826900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8336700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5174000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4881600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5518500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5219000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5247300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6182600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4643400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10561700</v>
+        <v>9474400</v>
       </c>
       <c r="E60" s="3">
-        <v>10640600</v>
+        <v>10824600</v>
       </c>
       <c r="F60" s="3">
-        <v>11298700</v>
+        <v>10905400</v>
       </c>
       <c r="G60" s="3">
-        <v>10164000</v>
+        <v>11580000</v>
       </c>
       <c r="H60" s="3">
-        <v>12616100</v>
+        <v>10417000</v>
       </c>
       <c r="I60" s="3">
-        <v>15130900</v>
+        <v>12930100</v>
       </c>
       <c r="J60" s="3">
+        <v>15507500</v>
+      </c>
+      <c r="K60" s="3">
         <v>19348900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18962300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18412800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14827200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15908000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17201000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12318300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10588400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8963300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10350600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12718900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10967800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11440200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11357000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12350800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11450500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11249900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9521900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8635900</v>
+        <v>8525200</v>
       </c>
       <c r="E61" s="3">
-        <v>8625100</v>
+        <v>8850800</v>
       </c>
       <c r="F61" s="3">
-        <v>8618600</v>
+        <v>8839800</v>
       </c>
       <c r="G61" s="3">
-        <v>8795800</v>
+        <v>8833100</v>
       </c>
       <c r="H61" s="3">
-        <v>9457200</v>
+        <v>9014800</v>
       </c>
       <c r="I61" s="3">
-        <v>9414000</v>
+        <v>9692600</v>
       </c>
       <c r="J61" s="3">
+        <v>9648300</v>
+      </c>
+      <c r="K61" s="3">
         <v>9987800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10084500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10854900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10382400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10311300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10897400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10944000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10215400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9427200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9955600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6896700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7957100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8107000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6550200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6260900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5806900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5052900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5035400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7958300</v>
+        <v>8127600</v>
       </c>
       <c r="E62" s="3">
-        <v>8069600</v>
+        <v>8156400</v>
       </c>
       <c r="F62" s="3">
-        <v>7175800</v>
+        <v>8270400</v>
       </c>
       <c r="G62" s="3">
-        <v>8043700</v>
+        <v>7354500</v>
       </c>
       <c r="H62" s="3">
-        <v>7822100</v>
+        <v>8243900</v>
       </c>
       <c r="I62" s="3">
-        <v>8130100</v>
+        <v>8016800</v>
       </c>
       <c r="J62" s="3">
+        <v>8332500</v>
+      </c>
+      <c r="K62" s="3">
         <v>9227000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8847300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9078000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9266900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9469200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9649000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9182400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8491900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7635800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8515600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8213500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8523300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9412800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8512400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8335100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8315800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6928000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6508900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>35073000</v>
+        <v>34126300</v>
       </c>
       <c r="E66" s="3">
-        <v>35041700</v>
+        <v>35946100</v>
       </c>
       <c r="F66" s="3">
-        <v>34788800</v>
+        <v>35913900</v>
       </c>
       <c r="G66" s="3">
-        <v>34786700</v>
+        <v>35654800</v>
       </c>
       <c r="H66" s="3">
-        <v>38045000</v>
+        <v>35652500</v>
       </c>
       <c r="I66" s="3">
-        <v>40756400</v>
+        <v>38992000</v>
       </c>
       <c r="J66" s="3">
+        <v>41770900</v>
+      </c>
+      <c r="K66" s="3">
         <v>46714300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45687100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45607700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41513400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>42509600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>44194800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39133300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>35438600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29841700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32870200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32113100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31943800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33628400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30806400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>31501900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>29637600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26852700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24489800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>17289000</v>
+        <v>16464500</v>
       </c>
       <c r="E72" s="3">
-        <v>17674800</v>
+        <v>17719400</v>
       </c>
       <c r="F72" s="3">
-        <v>16865400</v>
+        <v>18114800</v>
       </c>
       <c r="G72" s="3">
-        <v>16197500</v>
+        <v>17285200</v>
       </c>
       <c r="H72" s="3">
-        <v>17692100</v>
+        <v>16600700</v>
       </c>
       <c r="I72" s="3">
-        <v>17932100</v>
+        <v>18132500</v>
       </c>
       <c r="J72" s="3">
+        <v>18378400</v>
+      </c>
+      <c r="K72" s="3">
         <v>18769600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17224600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15043000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13671600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12888300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11960700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12032600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10195400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9106500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11379300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11564700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12445800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12920000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11727500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12038600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11306200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10196600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9765600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>20324700</v>
+        <v>19025200</v>
       </c>
       <c r="E76" s="3">
-        <v>19709800</v>
+        <v>20830600</v>
       </c>
       <c r="F76" s="3">
-        <v>19900000</v>
+        <v>20200400</v>
       </c>
       <c r="G76" s="3">
-        <v>19232100</v>
+        <v>20395300</v>
       </c>
       <c r="H76" s="3">
-        <v>20726700</v>
+        <v>19710800</v>
       </c>
       <c r="I76" s="3">
-        <v>20695400</v>
+        <v>21242700</v>
       </c>
       <c r="J76" s="3">
+        <v>21210500</v>
+      </c>
+      <c r="K76" s="3">
         <v>21804200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20281100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18100500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16809000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16713500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15718700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15791700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13704300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12793200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13900400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14084700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15190300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15749700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14445000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14799400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14083600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12754000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12299800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>505800</v>
+        <v>418700</v>
       </c>
       <c r="E81" s="3">
-        <v>255000</v>
+        <v>518400</v>
       </c>
       <c r="F81" s="3">
-        <v>510100</v>
+        <v>261400</v>
       </c>
       <c r="G81" s="3">
-        <v>410700</v>
+        <v>522800</v>
       </c>
       <c r="H81" s="3">
-        <v>421500</v>
+        <v>420900</v>
       </c>
       <c r="I81" s="3">
-        <v>332900</v>
+        <v>432000</v>
       </c>
       <c r="J81" s="3">
+        <v>341100</v>
+      </c>
+      <c r="K81" s="3">
         <v>900200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2118500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>594100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>583200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>300500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>658100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>691900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1875100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-505500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>26200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-173500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>414400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>520600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>638800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>423500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>719200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>244800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>222900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>445800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>348900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>491400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>798900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>671100</v>
+        <v>829600</v>
       </c>
       <c r="E83" s="3">
-        <v>702500</v>
+        <v>687800</v>
       </c>
       <c r="F83" s="3">
+        <v>719900</v>
+      </c>
+      <c r="G83" s="3">
+        <v>727700</v>
+      </c>
+      <c r="H83" s="3">
+        <v>743200</v>
+      </c>
+      <c r="I83" s="3">
         <v>710000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
+        <v>1002400</v>
+      </c>
+      <c r="K83" s="3">
         <v>725100</v>
       </c>
-      <c r="H83" s="3">
-        <v>692700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>978000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>725100</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>528800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>658300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2122700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>747400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>688800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>668700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>558500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1434400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>593500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>775600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>758800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>738700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>723500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>672300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>589100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>505100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>529200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>494100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>596900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>548700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>584600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>500400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1970100</v>
+        <v>1309200</v>
       </c>
       <c r="E89" s="3">
-        <v>1180100</v>
+        <v>2019200</v>
       </c>
       <c r="F89" s="3">
-        <v>1842600</v>
+        <v>1209500</v>
       </c>
       <c r="G89" s="3">
-        <v>244200</v>
+        <v>1888500</v>
       </c>
       <c r="H89" s="3">
-        <v>2902800</v>
+        <v>250300</v>
       </c>
       <c r="I89" s="3">
-        <v>1554000</v>
+        <v>2975000</v>
       </c>
       <c r="J89" s="3">
+        <v>1592700</v>
+      </c>
+      <c r="K89" s="3">
         <v>3438800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>503800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2910700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3017100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1731700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1652600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1125700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>677200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>822000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>592400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1225100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1145200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1316900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1334000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1035900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1318900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1075500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1353800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>832500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>888600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>718400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-785000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-815000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-947000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-861000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-821000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-858000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-910000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-735000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-651000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-647000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-758000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-579000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-657000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-570300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-562500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-402700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-462500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-637100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-706300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-665200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-578800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-619600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-671900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-886200</v>
+        <v>-860600</v>
       </c>
       <c r="E94" s="3">
-        <v>-1086100</v>
+        <v>-908200</v>
       </c>
       <c r="F94" s="3">
-        <v>-271300</v>
+        <v>-1113100</v>
       </c>
       <c r="G94" s="3">
-        <v>-850500</v>
+        <v>-278000</v>
       </c>
       <c r="H94" s="3">
-        <v>-1063400</v>
+        <v>-871700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1014800</v>
+        <v>-1089900</v>
       </c>
       <c r="J94" s="3">
+        <v>-1040000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-967200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1115300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-499800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-641800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-118500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-688800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-440100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-472400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-699300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-744800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-488200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-886000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-495100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>379200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>445400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8585,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-320100</v>
       </c>
       <c r="E96" s="3">
-        <v>-436600</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-38900</v>
+        <v>-447500</v>
       </c>
       <c r="G96" s="3">
-        <v>-2045800</v>
+        <v>-39900</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-2096700</v>
       </c>
       <c r="I96" s="3">
-        <v>609500</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>624700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-303700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-91100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-35500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-451800</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-240000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>115600</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-908200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>85200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-760900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>59500</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-87500</v>
+        <v>-3256300</v>
       </c>
       <c r="E100" s="3">
-        <v>-931600</v>
+        <v>-89700</v>
       </c>
       <c r="F100" s="3">
-        <v>-120000</v>
+        <v>-954800</v>
       </c>
       <c r="G100" s="3">
-        <v>-2909200</v>
+        <v>-122900</v>
       </c>
       <c r="H100" s="3">
-        <v>-114600</v>
+        <v>-2981700</v>
       </c>
       <c r="I100" s="3">
-        <v>-13000</v>
+        <v>-117400</v>
       </c>
       <c r="J100" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1305500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-527700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-66800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>203100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-687200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1201900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3212700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-661100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-640900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1214000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-818800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-275100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>288600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>886400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>191300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
-        <v>-6500</v>
-      </c>
       <c r="F101" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="K101" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="O101" s="3">
         <v>-4300</v>
       </c>
-      <c r="G101" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-18400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>5400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>3300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-68600</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="T101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="X101" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-10800</v>
       </c>
-      <c r="N101" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-24900</v>
-      </c>
-      <c r="S101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-41500</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="W101" s="3">
-        <v>5900</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7900</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-11200</v>
       </c>
       <c r="AE101" s="3">
         <v>-11200</v>
       </c>
       <c r="AF101" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>997500</v>
+        <v>-2808900</v>
       </c>
       <c r="E102" s="3">
-        <v>-844000</v>
+        <v>1022300</v>
       </c>
       <c r="F102" s="3">
-        <v>1447100</v>
+        <v>-865000</v>
       </c>
       <c r="G102" s="3">
-        <v>-3523100</v>
+        <v>1483100</v>
       </c>
       <c r="H102" s="3">
-        <v>1716200</v>
+        <v>-3610800</v>
       </c>
       <c r="I102" s="3">
-        <v>507900</v>
+        <v>1758900</v>
       </c>
       <c r="J102" s="3">
+        <v>520600</v>
+      </c>
+      <c r="K102" s="3">
         <v>1171500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>583200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1055500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1073300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1018700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-356500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>630600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1558900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3333800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-176700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-255700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-654100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>32900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-434200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>723900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>527200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>350300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>493700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>796600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>663200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>496500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
   <si>
     <t>OMVKY</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>9507600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>9051300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>11128100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>10487900</v>
-      </c>
-      <c r="H8" s="3">
-        <v>9949600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>12143700</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="3">
         <v>16068000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18555600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16096300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17222400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14471700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9165500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7687400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6801900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4943100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3836100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3423300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5192700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7090800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7287500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7099600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6463100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7854500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6210300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6265200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>6532600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>6125000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>7847300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>7269200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>7224900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>8921700</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="3">
         <v>12383000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12835500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11628500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10985500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9568300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6578800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5091100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4397000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3634500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2510700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2211300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3708000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4687200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4695400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4537400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4302700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5203600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4239900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4662100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>2975000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2926300</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3280700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3218700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2724700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3222000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="3">
         <v>3685000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5720100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4467700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6237000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4903400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2586700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2596300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2404800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1308600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1325400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1212000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1484700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2403700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2592100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2562200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2160300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2650900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1970400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1603100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>26600</v>
-      </c>
-      <c r="E12" s="3">
-        <v>18800</v>
-      </c>
-      <c r="F12" s="3">
-        <v>125200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>42100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>29900</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="3">
+        <v>117400</v>
+      </c>
+      <c r="L12" s="3">
+        <v>60500</v>
+      </c>
+      <c r="M12" s="3">
+        <v>84900</v>
+      </c>
+      <c r="N12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="O12" s="3">
+        <v>164800</v>
+      </c>
+      <c r="P12" s="3">
+        <v>48500</v>
+      </c>
+      <c r="Q12" s="3">
         <v>47600</v>
       </c>
-      <c r="J12" s="3">
-        <v>117400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>60500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>84900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>10900</v>
-      </c>
-      <c r="N12" s="3">
-        <v>164800</v>
-      </c>
-      <c r="O12" s="3">
-        <v>48500</v>
-      </c>
-      <c r="P12" s="3">
-        <v>47600</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>40200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>43900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>674600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>90500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>129800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>85200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>46500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>83500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>55000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>71000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>27700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>58200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>40600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>107700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>39300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>65100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>35900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>83300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,44 +1358,47 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>136200</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>77500</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>6500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-171900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1102200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1391,11 +1411,11 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
@@ -1412,139 +1432,145 @@
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-158500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>165000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-68100</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-153700</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>686700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>686700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>628000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>723300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>652400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>675600</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="3">
         <v>914900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>680800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>182800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>646300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2002300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>721500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>654900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>649600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>342100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>986000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>536700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>690500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>728500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>719100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>677600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>656700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>553600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>495100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>516100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>486400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>511600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>538600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>518400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>509400</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI15" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>8362400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>7787500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>9764600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>9080100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>8722400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>10713800</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="3">
         <v>14136300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14924500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12480500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15105000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12857400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8184400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6549000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5756600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3494900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4510700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3330500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5054200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6229300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6264600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5986700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5652000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6430200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5483700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5738100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1145300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1263800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1363500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1407800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1227200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1429900</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="3">
         <v>1931700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3631200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3615800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2117400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1614200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>981100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1138400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1045300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1448200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-674600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>92700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>138500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>861500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1022900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1112900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>811000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1424200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>726600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>527000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>868500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>604800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>631700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>186100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>219300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-58700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>183900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-198300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>203800</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="3">
         <v>33200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>61600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>489600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>293800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>139800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>218600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>219000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>212700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>84800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>57100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>52400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-51300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>131900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>144500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>227000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>161500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>88700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>154000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>176800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>90000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>25800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>225500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>113300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>149200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>118600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>2160900</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2170900</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2024700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2319300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1772200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>2343700</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="3">
         <v>2967300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4417900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4634200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3069500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3876700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1947000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2046200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1926600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2091500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>816800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>738500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>862900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1752300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1906100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2063400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1644800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2102000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1385600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1233100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>113000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>107400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>117400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>126300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>101900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>113000</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
         <v>118500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>111300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>120800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>103400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>90000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>105500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>80400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>81500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>70800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>73700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>68700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>81800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>85200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>95500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>90600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>89700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>82800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>77500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>94400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>70300</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF22" s="3">
         <v>80800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>69600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>68400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>74000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>1218400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1375600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1187300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1465400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>927100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1520700</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="3">
         <v>1846400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3581400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3984600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2307900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1664100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1094100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1277000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1176500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1462200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-691200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>76400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>908200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1071900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1249300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>882800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1430100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>803000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>609400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>888300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>630600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>776400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>608100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>633500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>835100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>710000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>566000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>865000</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K24" s="3">
         <v>1351300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2112800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1251300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1376400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>930200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>572900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>422100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>293100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-478800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-216900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>79600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>373600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>416500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>475300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>289500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>492100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>366600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>306300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>305200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>159300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>166100</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>193000</v>
       </c>
       <c r="AG24" s="3">
         <v>193000</v>
       </c>
       <c r="AH24" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AI24" s="3">
         <v>120900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>610300</v>
-      </c>
-      <c r="E26" s="3">
-        <v>742100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>352200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>755400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>361100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>655700</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="3">
         <v>495100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1468700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2733300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>931400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>733900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>521200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>854900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>883400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1940900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-474300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>62200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-74200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>534700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>655400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>774100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>593300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>938000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>436400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>303000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>583000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>471200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>610400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>915500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>418700</v>
-      </c>
-      <c r="E27" s="3">
-        <v>518400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>261400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>522800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>420900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>432000</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K27" s="3">
         <v>341100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>900200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2118500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>594100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>583200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>300500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>658100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>691900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1875100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-505500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-173500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>414400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>520600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>638800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>423500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>719200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>244800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>222900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>445800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>348900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>491400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>798900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,31 +2783,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-186100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-219300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>58700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-183900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>198300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-203800</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="3">
         <v>-33200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-61600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-489600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-293800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-139800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-218600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-219000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-212700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-84800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-57100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-52400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>51300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-131900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-144500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-227000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-161500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-88700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>418700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>518400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>261400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>522800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>420900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>432000</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" s="3">
         <v>341100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>900200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2118500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>594100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>583200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>300500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>658100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>691900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1875100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-505500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-173500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>414400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>520600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>638800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>423500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>719200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>244800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>222900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>445800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>348900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>491400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>798900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>418700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>518400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>261400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>522800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>420900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>432000</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="3">
         <v>341100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>900200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2118500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>594100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>583200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>300500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>658100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>691900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1875100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-505500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-173500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>414400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>520600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>638800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>423500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>719200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>244800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>222900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>445800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>348900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>491400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>798900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,917 +3698,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5864700</v>
+        <v>6462200</v>
       </c>
       <c r="E41" s="3">
-        <v>8675800</v>
+        <v>5673400</v>
       </c>
       <c r="F41" s="3">
-        <v>7664600</v>
+        <v>8450700</v>
       </c>
       <c r="G41" s="3">
-        <v>8621600</v>
+        <v>7648900</v>
       </c>
       <c r="H41" s="3">
-        <v>6928000</v>
+        <v>8238800</v>
       </c>
       <c r="I41" s="3">
-        <v>10477900</v>
+        <v>6828600</v>
       </c>
       <c r="J41" s="3">
+        <v>10278100</v>
+      </c>
+      <c r="K41" s="3">
         <v>8960500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8222000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7118400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6550400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5474700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4373300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3271300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3625800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2846600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7608800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6360000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3020700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3421700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3867300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4342100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4382900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4762400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3780200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3213800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1520700</v>
+        <v>1270400</v>
       </c>
       <c r="E42" s="3">
-        <v>1984800</v>
+        <v>1471100</v>
       </c>
       <c r="F42" s="3">
-        <v>2359200</v>
+        <v>1933300</v>
       </c>
       <c r="G42" s="3">
-        <v>2473300</v>
+        <v>1528700</v>
       </c>
       <c r="H42" s="3">
-        <v>2362500</v>
+        <v>2363500</v>
       </c>
       <c r="I42" s="3">
-        <v>2235100</v>
+        <v>2328600</v>
       </c>
       <c r="J42" s="3">
+        <v>2192500</v>
+      </c>
+      <c r="K42" s="3">
         <v>4351800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8071700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8400100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8005200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5580900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6690800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9531500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3779200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3010200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3291200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>5491600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6987300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3643500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2736600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3435100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2978500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3225800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4229900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2617600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>905400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>821300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3287400</v>
+        <v>3074900</v>
       </c>
       <c r="E43" s="3">
-        <v>3778000</v>
+        <v>3180100</v>
       </c>
       <c r="F43" s="3">
-        <v>3879900</v>
+        <v>3680000</v>
       </c>
       <c r="G43" s="3">
-        <v>3439100</v>
+        <v>4100800</v>
       </c>
       <c r="H43" s="3">
-        <v>3081300</v>
+        <v>3286400</v>
       </c>
       <c r="I43" s="3">
-        <v>4417100</v>
+        <v>3037100</v>
       </c>
       <c r="J43" s="3">
+        <v>4332900</v>
+      </c>
+      <c r="K43" s="3">
         <v>4783700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6224800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5761500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5860500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5014000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3793900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4157900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4349400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3343300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1941900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1843600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2862500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3564100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3807300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3585700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4357800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4056200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3196500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2945900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4242100</v>
+        <v>4278400</v>
       </c>
       <c r="E44" s="3">
-        <v>4208900</v>
+        <v>4103700</v>
       </c>
       <c r="F44" s="3">
-        <v>3908700</v>
+        <v>4099700</v>
       </c>
       <c r="G44" s="3">
-        <v>4433700</v>
+        <v>3900700</v>
       </c>
       <c r="H44" s="3">
-        <v>4488000</v>
+        <v>4236900</v>
       </c>
       <c r="I44" s="3">
-        <v>4462500</v>
+        <v>4423600</v>
       </c>
       <c r="J44" s="3">
+        <v>4377400</v>
+      </c>
+      <c r="K44" s="3">
         <v>5354100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5751500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5589600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4256600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3414900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3245800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2706400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2507500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2345900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1541300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1538200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1572000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2153900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2370400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1909300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2075400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1858300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1845300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1639300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1156300</v>
+        <v>3417400</v>
       </c>
       <c r="E45" s="3">
-        <v>1514100</v>
+        <v>3196200</v>
       </c>
       <c r="F45" s="3">
-        <v>1495300</v>
+        <v>3336900</v>
       </c>
       <c r="G45" s="3">
-        <v>1027900</v>
+        <v>3838800</v>
       </c>
       <c r="H45" s="3">
-        <v>960300</v>
+        <v>1079600</v>
       </c>
       <c r="I45" s="3">
-        <v>1058900</v>
+        <v>2438900</v>
       </c>
       <c r="J45" s="3">
+        <v>2999800</v>
+      </c>
+      <c r="K45" s="3">
         <v>1806500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1022300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>805200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>768200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>674300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>525500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>431700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>538500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>534600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>273000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>293500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>370900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>347900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>286600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>294100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>330200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>312300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>418700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>424900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>362300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>297300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>269300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>286100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>280500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>232400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>16071300</v>
+        <v>18503200</v>
       </c>
       <c r="E46" s="3">
-        <v>20161600</v>
+        <v>17624600</v>
       </c>
       <c r="F46" s="3">
-        <v>19307700</v>
+        <v>21500700</v>
       </c>
       <c r="G46" s="3">
-        <v>19995500</v>
+        <v>21116400</v>
       </c>
       <c r="H46" s="3">
-        <v>17820200</v>
+        <v>19205100</v>
       </c>
       <c r="I46" s="3">
-        <v>22651500</v>
+        <v>19056800</v>
       </c>
       <c r="J46" s="3">
+        <v>24180800</v>
+      </c>
+      <c r="K46" s="3">
         <v>25256600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29292400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>27674700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25440900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20158800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18629300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20098800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14800400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12080500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14656200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15526900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14813500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13131000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13068200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13566200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14124700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14214900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13470600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10841700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9234100</v>
+        <v>9039700</v>
       </c>
       <c r="E47" s="3">
-        <v>8959400</v>
+        <v>8932800</v>
       </c>
       <c r="F47" s="3">
-        <v>9272800</v>
+        <v>8726900</v>
       </c>
       <c r="G47" s="3">
-        <v>9611800</v>
+        <v>8032500</v>
       </c>
       <c r="H47" s="3">
-        <v>9570800</v>
+        <v>9185000</v>
       </c>
       <c r="I47" s="3">
-        <v>9749100</v>
+        <v>9433400</v>
       </c>
       <c r="J47" s="3">
+        <v>9563200</v>
+      </c>
+      <c r="K47" s="3">
         <v>10292900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12286500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11576300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11807000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11509900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13968500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13733900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13026100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11737400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7767600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8480700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8646600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8831500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9770500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6566700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6554000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6707000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5998800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5680000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22025700</v>
+        <v>22432500</v>
       </c>
       <c r="E48" s="3">
-        <v>22132100</v>
+        <v>21307200</v>
       </c>
       <c r="F48" s="3">
-        <v>22241700</v>
+        <v>21557900</v>
       </c>
       <c r="G48" s="3">
-        <v>22473200</v>
+        <v>22196300</v>
       </c>
       <c r="H48" s="3">
-        <v>22661500</v>
+        <v>21475400</v>
       </c>
       <c r="I48" s="3">
-        <v>21485200</v>
+        <v>22336200</v>
       </c>
       <c r="J48" s="3">
+        <v>21075600</v>
+      </c>
+      <c r="K48" s="3">
         <v>21395500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20763500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20747900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20447600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20130700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19727700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19286300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19232300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19153100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14920900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16464000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16726900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19237700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20358100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19369400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19616500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>17879500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>15679200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15670700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2143200</v>
+        <v>2288600</v>
       </c>
       <c r="E49" s="3">
-        <v>2108900</v>
+        <v>2073300</v>
       </c>
       <c r="F49" s="3">
-        <v>1970400</v>
+        <v>2054200</v>
       </c>
       <c r="G49" s="3">
-        <v>2423400</v>
+        <v>1329700</v>
       </c>
       <c r="H49" s="3">
-        <v>2390200</v>
+        <v>2315800</v>
       </c>
       <c r="I49" s="3">
-        <v>2867600</v>
+        <v>2355900</v>
       </c>
       <c r="J49" s="3">
+        <v>2812900</v>
+      </c>
+      <c r="K49" s="3">
         <v>2780100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2888700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2820400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2798600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3426800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3611900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3541100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3695600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3434000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3190500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4212000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4215300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4859900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5203800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4843200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5048000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3923700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3202100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3188600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3677200</v>
+        <v>235300</v>
       </c>
       <c r="E52" s="3">
-        <v>3414700</v>
+        <v>223900</v>
       </c>
       <c r="F52" s="3">
-        <v>3321700</v>
+        <v>225500</v>
       </c>
       <c r="G52" s="3">
-        <v>1546200</v>
+        <v>392400</v>
       </c>
       <c r="H52" s="3">
-        <v>2920700</v>
+        <v>113300</v>
       </c>
       <c r="I52" s="3">
-        <v>3481200</v>
+        <v>119000</v>
       </c>
       <c r="J52" s="3">
+        <v>132600</v>
+      </c>
+      <c r="K52" s="3">
         <v>3256300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3287500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3149000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3214200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3096200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3285600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3253400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4170600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2737900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2099700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2086900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1795600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1074000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>977500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>905800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>958200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>996000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1256000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1408700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>935700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>53151500</v>
+        <v>53789900</v>
       </c>
       <c r="E54" s="3">
-        <v>56776700</v>
+        <v>51417600</v>
       </c>
       <c r="F54" s="3">
-        <v>56114300</v>
+        <v>55303700</v>
       </c>
       <c r="G54" s="3">
-        <v>56050100</v>
+        <v>55999800</v>
       </c>
       <c r="H54" s="3">
-        <v>55363400</v>
+        <v>53561600</v>
       </c>
       <c r="I54" s="3">
-        <v>60234600</v>
+        <v>54568800</v>
       </c>
       <c r="J54" s="3">
+        <v>59086300</v>
+      </c>
+      <c r="K54" s="3">
         <v>62981500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68518500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65968200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>63708300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58322400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>59223000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59913500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>54925000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>49142900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42634900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>46770600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>46197900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>47134200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>49378100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>45251400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>46301300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43721200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>39606700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36789600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3961900</v>
+        <v>3841200</v>
       </c>
       <c r="E57" s="3">
-        <v>4191200</v>
+        <v>3832600</v>
       </c>
       <c r="F57" s="3">
-        <v>4380600</v>
+        <v>4082400</v>
       </c>
       <c r="G57" s="3">
-        <v>4572200</v>
+        <v>4371600</v>
       </c>
       <c r="H57" s="3">
-        <v>4181200</v>
+        <v>4369200</v>
       </c>
       <c r="I57" s="3">
-        <v>4564400</v>
+        <v>4121200</v>
       </c>
       <c r="J57" s="3">
+        <v>4477400</v>
+      </c>
+      <c r="K57" s="3">
         <v>5824900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6514500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5991100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6072700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5268700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4034100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4424600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4777900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4292800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2667400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2607300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3769100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4850600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4789700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4173900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5197500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5205900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4101400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3877000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1134200</v>
+        <v>1236900</v>
       </c>
       <c r="E58" s="3">
-        <v>1289200</v>
+        <v>1097200</v>
       </c>
       <c r="F58" s="3">
-        <v>1271500</v>
+        <v>1255800</v>
       </c>
       <c r="G58" s="3">
-        <v>1719000</v>
+        <v>1268900</v>
       </c>
       <c r="H58" s="3">
-        <v>1545100</v>
+        <v>1642700</v>
       </c>
       <c r="I58" s="3">
-        <v>1715700</v>
+        <v>1522900</v>
       </c>
       <c r="J58" s="3">
+        <v>1683000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1742300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1111000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2053200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1191500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1383300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1852300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1045300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1936100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1689600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>855200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>916400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>613100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>943300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1768900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1664600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1934300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>997200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>965800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1001400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>274900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>218800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>190700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>305200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4378300</v>
+        <v>5093700</v>
       </c>
       <c r="E59" s="3">
-        <v>5344200</v>
+        <v>4839800</v>
       </c>
       <c r="F59" s="3">
-        <v>5253300</v>
+        <v>5877700</v>
       </c>
       <c r="G59" s="3">
-        <v>5288800</v>
+        <v>4458900</v>
       </c>
       <c r="H59" s="3">
-        <v>4690700</v>
+        <v>5114300</v>
       </c>
       <c r="I59" s="3">
-        <v>6650000</v>
+        <v>5109200</v>
       </c>
       <c r="J59" s="3">
+        <v>7136000</v>
+      </c>
+      <c r="K59" s="3">
         <v>7940400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11723400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10918000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11148700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8175200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10021600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11731100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5604200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4606000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5440700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6826900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8336700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5174000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4881600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5518500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5219000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5247300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6182600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4643400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9474400</v>
+        <v>10171800</v>
       </c>
       <c r="E60" s="3">
-        <v>10824600</v>
+        <v>9769600</v>
       </c>
       <c r="F60" s="3">
-        <v>10905400</v>
+        <v>11215900</v>
       </c>
       <c r="G60" s="3">
-        <v>11580000</v>
+        <v>11569600</v>
       </c>
       <c r="H60" s="3">
-        <v>10417000</v>
+        <v>11126200</v>
       </c>
       <c r="I60" s="3">
-        <v>12930100</v>
+        <v>10753300</v>
       </c>
       <c r="J60" s="3">
+        <v>13296400</v>
+      </c>
+      <c r="K60" s="3">
         <v>15507500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19348900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18962300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18412800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14827200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15908000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17201000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12318300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10588400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8963300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10350600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12718900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10967800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11440200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11357000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12350800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11450500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11249900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9521900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8525200</v>
+        <v>9092100</v>
       </c>
       <c r="E61" s="3">
-        <v>8850800</v>
+        <v>8247100</v>
       </c>
       <c r="F61" s="3">
-        <v>8839800</v>
+        <v>8621200</v>
       </c>
       <c r="G61" s="3">
-        <v>8833100</v>
+        <v>8821700</v>
       </c>
       <c r="H61" s="3">
-        <v>9014800</v>
+        <v>8440900</v>
       </c>
       <c r="I61" s="3">
-        <v>9692600</v>
+        <v>8885400</v>
       </c>
       <c r="J61" s="3">
+        <v>9507800</v>
+      </c>
+      <c r="K61" s="3">
         <v>9648300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9987800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10084500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10854900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10382400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10311300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10897400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10944000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10215400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9427200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9955600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6896700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7957100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8107000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6550200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6260900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5806900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5052900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5035400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8127600</v>
+        <v>5370300</v>
       </c>
       <c r="E62" s="3">
-        <v>8156400</v>
+        <v>5155900</v>
       </c>
       <c r="F62" s="3">
-        <v>8270400</v>
+        <v>5206600</v>
       </c>
       <c r="G62" s="3">
-        <v>7354500</v>
+        <v>5363100</v>
       </c>
       <c r="H62" s="3">
-        <v>8243900</v>
+        <v>4663400</v>
       </c>
       <c r="I62" s="3">
-        <v>8016800</v>
+        <v>5316600</v>
       </c>
       <c r="J62" s="3">
+        <v>4952200</v>
+      </c>
+      <c r="K62" s="3">
         <v>8332500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9227000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8847300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9078000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9266900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9469200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9649000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9182400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8491900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7635800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8515600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8213500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8523300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9412800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8512400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8335100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8315800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6928000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6508900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>34126300</v>
+        <v>26881600</v>
       </c>
       <c r="E66" s="3">
-        <v>35946100</v>
+        <v>25274800</v>
       </c>
       <c r="F66" s="3">
-        <v>35913900</v>
+        <v>27110800</v>
       </c>
       <c r="G66" s="3">
-        <v>35654800</v>
+        <v>27958400</v>
       </c>
       <c r="H66" s="3">
-        <v>35652500</v>
+        <v>26534700</v>
       </c>
       <c r="I66" s="3">
-        <v>38992000</v>
+        <v>27278400</v>
       </c>
       <c r="J66" s="3">
+        <v>30055400</v>
+      </c>
+      <c r="K66" s="3">
         <v>41770900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46714300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45687100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45607700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41513400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42509600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>44194800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39133300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>35438600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29841700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32870200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32113100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>31943800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33628400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>30806400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>31501900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29637600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26852700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24489800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>16464500</v>
+        <v>15848800</v>
       </c>
       <c r="E72" s="3">
-        <v>17719400</v>
+        <v>15053000</v>
       </c>
       <c r="F72" s="3">
-        <v>18114800</v>
+        <v>16529300</v>
       </c>
       <c r="G72" s="3">
-        <v>17285200</v>
+        <v>16397700</v>
       </c>
       <c r="H72" s="3">
-        <v>16600700</v>
+        <v>15536600</v>
       </c>
       <c r="I72" s="3">
-        <v>18132500</v>
+        <v>15520700</v>
       </c>
       <c r="J72" s="3">
+        <v>16823100</v>
+      </c>
+      <c r="K72" s="3">
         <v>18378400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18769600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17224600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15043000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13671600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12888300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11960700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12032600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10195400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9106500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11379300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11564700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12445800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12920000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11727500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12038600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11306200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10196600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9765600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19025200</v>
+        <v>18939300</v>
       </c>
       <c r="E76" s="3">
-        <v>20830600</v>
+        <v>18404600</v>
       </c>
       <c r="F76" s="3">
-        <v>20200400</v>
+        <v>20289100</v>
       </c>
       <c r="G76" s="3">
-        <v>20395300</v>
+        <v>20159200</v>
       </c>
       <c r="H76" s="3">
-        <v>19710800</v>
+        <v>19489800</v>
       </c>
       <c r="I76" s="3">
-        <v>21242700</v>
+        <v>19427900</v>
       </c>
       <c r="J76" s="3">
+        <v>20837700</v>
+      </c>
+      <c r="K76" s="3">
         <v>21210500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21804200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20281100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18100500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16809000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16713500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15718700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15791700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13704300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12793200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13900400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14084700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15190300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15749700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14445000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14799400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14083600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12754000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12299800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>418700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>518400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>261400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>522800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>420900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>432000</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K81" s="3">
         <v>341100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>900200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2118500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>594100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>583200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>300500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>658100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>691900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1875100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-505500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-173500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>414400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>520600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>638800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>423500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>719200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>244800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>222900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>445800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>348900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>491400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>798900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>829600</v>
+        <v>710200</v>
       </c>
       <c r="E83" s="3">
-        <v>687800</v>
+        <v>655000</v>
       </c>
       <c r="F83" s="3">
-        <v>719900</v>
+        <v>696400</v>
       </c>
       <c r="G83" s="3">
-        <v>727700</v>
+        <v>416800</v>
       </c>
       <c r="H83" s="3">
-        <v>743200</v>
+        <v>702100</v>
       </c>
       <c r="I83" s="3">
-        <v>710000</v>
+        <v>660700</v>
       </c>
       <c r="J83" s="3">
+        <v>662100</v>
+      </c>
+      <c r="K83" s="3">
         <v>1002400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>725100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>528800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>658300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2122700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>747400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>688800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>668700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>558500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1434400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>593500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>775600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>758800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>738700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>723500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>672300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>589100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>505100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>529200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>494100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>596900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>548700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>584600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>500400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1309200</v>
+        <v>1584900</v>
       </c>
       <c r="E89" s="3">
-        <v>2019200</v>
+        <v>1266500</v>
       </c>
       <c r="F89" s="3">
-        <v>1209500</v>
+        <v>1966800</v>
       </c>
       <c r="G89" s="3">
-        <v>1888500</v>
+        <v>1207000</v>
       </c>
       <c r="H89" s="3">
-        <v>250300</v>
+        <v>1804600</v>
       </c>
       <c r="I89" s="3">
-        <v>2975000</v>
+        <v>246700</v>
       </c>
       <c r="J89" s="3">
+        <v>2918300</v>
+      </c>
+      <c r="K89" s="3">
         <v>1592700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3438800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>503800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2910700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3017100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1731700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1652600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1125700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>677200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>822000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>592400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1225100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1145200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1316900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1334000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1035900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1318900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1075500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1353800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>832500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>888600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>718400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-785000</v>
+        <v>-988200</v>
       </c>
       <c r="E91" s="3">
-        <v>-815000</v>
+        <v>-842200</v>
       </c>
       <c r="F91" s="3">
-        <v>-947000</v>
+        <v>-878200</v>
       </c>
       <c r="G91" s="3">
-        <v>-861000</v>
+        <v>-1046800</v>
       </c>
       <c r="H91" s="3">
-        <v>-821000</v>
+        <v>-911300</v>
       </c>
       <c r="I91" s="3">
-        <v>-858000</v>
+        <v>-896300</v>
       </c>
       <c r="J91" s="3">
+        <v>-932200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-910000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-735000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-651000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-647000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-758000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-579000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-657000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-570300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-562500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-402700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-462500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-637100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-706300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-665200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-578800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-619600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-671900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-860600</v>
+        <v>-1315000</v>
       </c>
       <c r="E94" s="3">
-        <v>-908200</v>
+        <v>-832500</v>
       </c>
       <c r="F94" s="3">
-        <v>-1113100</v>
+        <v>-884700</v>
       </c>
       <c r="G94" s="3">
-        <v>-278000</v>
+        <v>-1110900</v>
       </c>
       <c r="H94" s="3">
-        <v>-871700</v>
+        <v>-265700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1089900</v>
+        <v>-859200</v>
       </c>
       <c r="J94" s="3">
+        <v>-1069100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-967200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1115300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-499800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-641800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-118500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-688800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-440100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-472400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-699300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-744800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-488200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-886000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-495100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>379200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>445400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-320100</v>
+        <v>36800</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>1782900</v>
       </c>
       <c r="F96" s="3">
-        <v>-447500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-39900</v>
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H96" s="3">
-        <v>-2096700</v>
+        <v>34900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>1819900</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>624700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-303700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-91100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-35500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-451800</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-240000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>115600</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-908200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>85200</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-760900</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>59500</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3256300</v>
+        <v>291100</v>
       </c>
       <c r="E100" s="3">
-        <v>-89700</v>
+        <v>-3150100</v>
       </c>
       <c r="F100" s="3">
-        <v>-954800</v>
+        <v>-87400</v>
       </c>
       <c r="G100" s="3">
-        <v>-122900</v>
+        <v>-952800</v>
       </c>
       <c r="H100" s="3">
-        <v>-2981700</v>
+        <v>-117500</v>
       </c>
       <c r="I100" s="3">
-        <v>-117400</v>
+        <v>-2938900</v>
       </c>
       <c r="J100" s="3">
+        <v>-115200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-13300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1305500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-527700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-66800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>203100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-687200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1201900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3212700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-661100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-640900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1214000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-818800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-275100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>288600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>886400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>191300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1100</v>
+        <v>-4200</v>
       </c>
       <c r="E101" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I101" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="L101" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="U101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="K101" s="3">
-        <v>5400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-68600</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="V101" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-10800</v>
       </c>
-      <c r="O101" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-24900</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-41500</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="X101" s="3">
-        <v>5900</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7900</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-11200</v>
       </c>
       <c r="AF101" s="3">
         <v>-11200</v>
       </c>
       <c r="AG101" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2808900</v>
+        <v>552100</v>
       </c>
       <c r="E102" s="3">
-        <v>1022300</v>
+        <v>-2718300</v>
       </c>
       <c r="F102" s="3">
-        <v>-865000</v>
+        <v>996900</v>
       </c>
       <c r="G102" s="3">
-        <v>1483100</v>
+        <v>-863300</v>
       </c>
       <c r="H102" s="3">
-        <v>-3610800</v>
+        <v>1417200</v>
       </c>
       <c r="I102" s="3">
-        <v>1758900</v>
+        <v>-3559000</v>
       </c>
       <c r="J102" s="3">
+        <v>1725300</v>
+      </c>
+      <c r="K102" s="3">
         <v>520600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1171500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>583200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1055500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1073300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1018700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-356500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>630600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1558900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3333800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-176700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-255700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-654100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>32900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-434200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>723900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>527200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>350300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>493700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>796600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>663200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>496500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>OMVKY</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,86 +832,89 @@
       <c r="J8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="3">
         <v>16068000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18555600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16096300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17222400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14471700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9165500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7687400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6801900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4943100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3836100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3423300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5192700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7090800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7287500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7099600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6463100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7854500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6210300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6265200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,86 +939,89 @@
       <c r="J9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="3">
         <v>12383000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12835500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11628500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10985500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9568300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6578800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5091100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4397000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3634500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2510700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2211300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3708000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4687200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4695400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4537400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4302700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5203600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4239900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4662100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1037,86 +1046,89 @@
       <c r="J10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="3">
         <v>3685000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5720100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4467700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6237000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4903400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2586700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2596300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2404800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1308600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1325400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1212000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1484700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2403700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2592100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2562200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2160300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2650900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1970400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1603100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1179,86 +1192,89 @@
       <c r="J12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="3">
         <v>117400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>60500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>84900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>164800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>48500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>47600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>40200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>43900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>674600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>90500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>129800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>85200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>46500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>83500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>55000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>71000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>27700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>58200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>40600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>107700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>39300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>65100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>35900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>83300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1387,21 +1406,21 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>6500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-171900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1102200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1414,11 +1433,11 @@
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
@@ -1435,38 +1454,41 @@
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-158500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>165000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-68100</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-153700</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,86 +1513,89 @@
       <c r="J15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="3">
         <v>914900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>680800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>182800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>646300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2002300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>721500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>654900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>649600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>342100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>986000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>536700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>690500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>728500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>719100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>677600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>656700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>553600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>495100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>516100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>486400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>511600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>538600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>518400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>509400</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AJ15" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1630,86 +1656,89 @@
       <c r="J17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="3">
         <v>14136300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14924500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12480500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15105000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12857400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8184400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6549000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5756600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3494900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4510700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3330500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5054200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6229300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6264600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5986700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5652000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6430200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5483700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5738100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1734,86 +1763,89 @@
       <c r="J18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="3">
         <v>1931700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3631200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3615800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2117400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1614200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>981100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1138400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1045300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1448200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-674600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>92700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>138500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>861500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1022900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1112900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>811000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1424200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>726600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>527000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>868500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>604800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>631700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,86 +1909,89 @@
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
         <v>33200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>61600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>489600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>293800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>139800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>218600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>219000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>212700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>84800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>57100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>52400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-51300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>131900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>144500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>227000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>161500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>88700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>154000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>176800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>90000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>25800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>225500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>113300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>149200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>118600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1980,86 +2016,89 @@
       <c r="J21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3">
         <v>2967300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4417900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4634200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3069500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3876700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1947000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2046200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1926600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2091500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>816800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>738500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>862900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1752300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1906100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2063400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1644800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2102000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1385600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1233100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,86 +2123,89 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>118500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>111300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>120800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>103400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>90000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>105500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>80400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>81500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>70800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>73700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>68700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>81800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>85200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>95500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>90600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>89700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>82800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>77500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>94400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>70300</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG22" s="3">
         <v>80800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>69600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>68400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>74000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2188,86 +2230,89 @@
       <c r="J23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="3">
         <v>1846400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3581400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3984600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2307900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1664100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1094100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1277000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1176500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1462200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-691200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>76400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>908200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1071900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1249300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>882800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1430100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>803000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>609400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>888300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>630600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>776400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,86 +2337,89 @@
       <c r="J24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="3">
         <v>1351300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2112800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1251300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1376400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>930200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>572900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>422100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>293100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-478800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-216900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>79600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>373600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>416500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>475300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>289500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>492100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>366600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>306300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>305200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>159300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>166100</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>193000</v>
       </c>
       <c r="AH24" s="3">
         <v>193000</v>
       </c>
       <c r="AI24" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>120900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,8 +2522,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2500,86 +2551,89 @@
       <c r="J26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" s="3">
         <v>495100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1468700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2733300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>931400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>733900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>521200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>854900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>883400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1940900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-474300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>62200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-74200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>534700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>655400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>774100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>593300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>938000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>436400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>303000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>583000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>471200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>610400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>915500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,86 +2658,89 @@
       <c r="J27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="3">
         <v>341100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>900200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2118500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>594100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>583200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>300500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>658100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>691900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1875100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-505500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-173500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>414400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>520600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>638800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>423500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>719200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>244800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>222900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>445800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>348900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>491400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>798900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,8 +2872,8 @@
       <c r="J29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,86 +3193,89 @@
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3">
         <v>-33200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-61600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-489600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-293800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-139800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-218600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-219000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-212700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-84800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-57100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-52400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>51300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-131900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-144500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-227000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-161500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-88700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3228,86 +3300,89 @@
       <c r="J33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" s="3">
         <v>341100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>900200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2118500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>594100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>583200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>300500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>658100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>691900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1875100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-505500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-173500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>414400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>520600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>638800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>423500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>719200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>244800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>222900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>445800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>348900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>491400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>798900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,8 +3485,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3436,195 +3514,201 @@
       <c r="J35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" s="3">
         <v>341100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>900200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2118500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>594100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>583200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>300500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>658100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>691900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1875100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-505500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-173500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>414400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>520600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>638800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>423500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>719200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>244800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>222900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>445800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>348900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>491400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>798900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,944 +3784,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6400200</v>
+      </c>
+      <c r="E41" s="3">
         <v>6462200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5673400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8450700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7648900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8238800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6828600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10278100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8960500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8222000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7118400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6550400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5474700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4373300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3271300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3625800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2846600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7608800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6360000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3020700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3421700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3867300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4342100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4382900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4762400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3780200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3213800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1111900</v>
+      </c>
+      <c r="E42" s="3">
         <v>1270400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1471100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1933300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1528700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2363500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2328600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2192500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4351800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8071700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8400100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8005200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5580900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6690800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9531500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3779200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3010200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3291200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5491600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6987300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3643500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2736600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3435100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2978500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3225800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4229900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2617600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>905400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>821300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3016900</v>
+      </c>
+      <c r="E43" s="3">
         <v>3074900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3180100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3680000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4100800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3286400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3037100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4332900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4783700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6224800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5761500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5860500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5014000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3793900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4157900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4349400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3343300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1941900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1843600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2862500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3564100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3807300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3585700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4357800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4056200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3196500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2945900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4075000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4278400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4103700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4099700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3900700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4236900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4423600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4377400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5354100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5751500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5589600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4256600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3414900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3245800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2706400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2507500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2345900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1541300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1538200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1572000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2153900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2370400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1909300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2075400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1858300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1845300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1639300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2099600</v>
+      </c>
+      <c r="E45" s="3">
         <v>3417400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3196200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3336900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3838800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1079600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2438900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2999800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1806500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1022300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>805200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>768200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>674300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>525500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>431700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>538500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>534600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>273000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>293500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>370900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>347900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>286600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>294100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>330200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>312300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>418700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>424900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>362300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>297300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>269300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>286100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>280500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>232400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16703600</v>
+      </c>
+      <c r="E46" s="3">
         <v>18503200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17624600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21500700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21116400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19205100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19056800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24180800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25256600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29292400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27674700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25440900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20158800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18629300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20098800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14800400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12080500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14656200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15526900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14813500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13131000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13068200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13566200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14124700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14214900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13470600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10841700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9086900</v>
+      </c>
+      <c r="E47" s="3">
         <v>9039700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8932800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8726900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8032500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9185000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9433400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9563200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10292900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12286500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11576300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11807000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11509900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13968500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13733900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13026100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11737400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7767600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8480700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8646600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8831500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9770500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6566700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6554000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6707000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5998800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5680000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21147100</v>
+      </c>
+      <c r="E48" s="3">
         <v>22432500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21307200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21557900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22196300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21475400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22336200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21075600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21395500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20763500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20747900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20447600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20130700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19727700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19286300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19232300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19153100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14920900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16464000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16726900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19237700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20358100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19369400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19616500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>17879500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15679200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15670700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2094400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2288600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2073300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2054200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1329700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2315800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2355900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2812900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2780100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2888700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2820400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2798600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3426800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3611900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3541100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3695600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3434000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3190500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4212000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4215300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4859900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5203800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4843200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5048000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3923700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3202100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3188600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E52" s="3">
         <v>235300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>223900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>225500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>392400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>113300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>119000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>132600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3256300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3287500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3149000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3214200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3096200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3285600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3253400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4170600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2737900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2099700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2086900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1795600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1074000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>977500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>905800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>958200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>996000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1256000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1408700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>935700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50536300</v>
+      </c>
+      <c r="E54" s="3">
         <v>53789900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51417600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>55303700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>55999800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>53561600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54568800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>59086300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62981500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68518500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65968200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63708300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58322400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59223000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>59913500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>54925000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49142900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42634900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>46770600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>46197900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>47134200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>49378100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>45251400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>46301300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43721200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>39606700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>36789600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3854400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3841200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3832600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4082400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4371600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4369200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4121200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4477400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5824900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6514500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5991100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6072700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5268700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4034100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4424600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4777900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4292800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2667400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2607300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3769100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4850600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4789700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4173900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5197500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5205900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4101400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3877000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1486700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1236900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1097200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1255800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1268900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1642700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1522900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1683000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1742300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1111000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2053200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1191500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1383300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1852300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1045300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1936100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1689600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>855200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>916400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>613100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>943300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1768900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1664600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1934300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>997200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>965800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1001400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>274900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>218800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>190700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>305200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4451800</v>
+      </c>
+      <c r="E59" s="3">
         <v>5093700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4839800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5877700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4458900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5114300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5109200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7136000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7940400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11723400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10918000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11148700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8175200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10021600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11731100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5604200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4606000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5440700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6826900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8336700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5174000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4881600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5518500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5219000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5247300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6182600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4643400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9792900</v>
+      </c>
+      <c r="E60" s="3">
         <v>10171800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9769600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11215900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11569600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11126200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10753300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13296400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15507500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19348900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18962300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18412800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14827200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15908000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17201000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12318300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10588400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8963300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10350600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12718900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10967800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11440200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11357000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12350800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11450500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11249900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9521900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8252400</v>
+      </c>
+      <c r="E61" s="3">
         <v>9092100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8247100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8621200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8821700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8440900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8885400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9507800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9648300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9987800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10084500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10854900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10382400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10311300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10897400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10944000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10215400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9427200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9955600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6896700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7957100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8107000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6550200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6260900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5806900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5052900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5035400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4907300</v>
+      </c>
+      <c r="E62" s="3">
         <v>5370300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5155900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5206600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5363100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4663400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5316600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4952200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8332500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9227000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8847300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9078000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9266900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9469200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9649000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9182400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8491900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7635800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8515600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8213500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8523300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9412800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8512400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8335100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8315800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6928000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6508900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25050200</v>
+      </c>
+      <c r="E66" s="3">
         <v>26881600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25274800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27110800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27958400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26534700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27278400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30055400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>41770900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46714300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45687100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45607700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>41513400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>42509600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>44194800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39133300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35438600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29841700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32870200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32113100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>31943800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>33628400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30806400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>31501900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29637600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26852700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>24489800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15037800</v>
+      </c>
+      <c r="E72" s="3">
         <v>15848800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15053000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16529300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16397700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15536600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15520700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16823100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18378400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18769600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17224600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15043000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13671600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12888300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11960700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12032600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10195400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9106500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11379300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11564700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12445800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12920000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11727500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12038600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11306200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10196600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9765600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18498800</v>
+      </c>
+      <c r="E76" s="3">
         <v>18939300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18404600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20289100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20159200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19489800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19427900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20837700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21210500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21804200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20281100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18100500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16809000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16713500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15718700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15791700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13704300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12793200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13900400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14084700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15190300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15749700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14445000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14799400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14083600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12754000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12299800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,117 +7537,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7484,86 +7678,89 @@
       <c r="J81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L81" s="3">
         <v>341100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>900200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2118500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>594100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>583200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>300500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>658100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>691900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1875100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-505500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-173500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>414400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>520600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>638800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>423500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>719200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>244800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>222900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>445800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>348900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>491400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>798900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>446600</v>
+      </c>
+      <c r="E83" s="3">
         <v>710200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>655000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>696400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>416800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>702100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>660700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>662100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1002400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>725100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>528800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>658300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2122700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>747400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>688800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>668700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>558500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1434400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>593500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>775600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>758800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>738700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>723500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>672300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>589100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>505100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>529200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>494100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>596900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>548700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>584600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>500400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1066400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1584900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1266500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1966800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1207000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1804600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>246700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2918300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1592700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3438800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>503800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2910700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3017100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1731700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1652600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1125700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>677200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>822000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>592400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1225100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1145200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1316900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1334000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1035900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1318900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1075500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1353800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>832500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>888600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>718400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1063300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-988200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-842200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-878200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1046800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-911300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-896300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-932200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-910000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-735000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-651000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-647000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-758000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-579000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-657000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-570300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-562500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-402700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-462500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-637100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-706300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-665200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-578800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-619600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-671900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-389300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1315000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-832500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-884700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1110900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-265700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-859200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1069100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-967200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1115300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-499800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-641800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-118500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-688800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-440100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-472400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-699300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-744800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-488200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-886000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-495100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>379200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>445400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,112 +9052,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E96" s="3">
         <v>36800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1782900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3">
         <v>34900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1819900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>624700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-303700</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-91100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-35500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-451800</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-240000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>115600</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-908200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>85200</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-760900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>59500</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-385100</v>
+      </c>
+      <c r="E100" s="3">
         <v>291100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3150100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-87400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-952800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-117500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2938900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-115200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1305500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-527700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-66800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>203100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-687200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1201900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3212700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-661100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-640900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1214000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-818800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-275100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>288600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>886400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>191300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-18200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-71100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-18800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-68600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-24900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-41500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-15200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-13300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7900</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-11200</v>
       </c>
       <c r="AG101" s="3">
         <v>-11200</v>
       </c>
       <c r="AH101" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300200</v>
+      </c>
+      <c r="E102" s="3">
         <v>552100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2718300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>996900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-863300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1417200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3559000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1725300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>520600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1171500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>583200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1055500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1073300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1018700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-356500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>630600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1558900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3333800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-176700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-255700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-654100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-434200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>723900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>527200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>350300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>493700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>796600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>663200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>496500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>OMVKY</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,86 +839,89 @@
       <c r="K8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="3">
         <v>16068000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18555600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16096300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17222400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14471700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9165500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7687400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6801900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4943100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3836100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3423300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5192700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7090800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7287500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7099600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6463100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7854500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6210300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6265200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -942,86 +949,89 @@
       <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="3">
         <v>12383000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12835500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11628500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10985500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9568300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6578800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5091100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4397000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3634500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2510700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2211300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3708000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4687200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4695400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4537400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4302700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5203600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4239900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4662100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,86 +1059,89 @@
       <c r="K10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="3">
         <v>3685000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5720100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4467700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6237000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4903400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2586700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2596300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2404800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1308600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1325400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1212000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1484700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2403700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2592100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2562200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2160300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2650900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1970400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1603100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1195,86 +1209,89 @@
       <c r="K12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="3">
         <v>117400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>60500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>84900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>164800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>48500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>47600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>40200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>674600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>90500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>129800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>85200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>46500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>83500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>55000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>71000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>27700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>58200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>40600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>107700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>39300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>65100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>35900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>83300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1409,21 +1429,21 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>6500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-171900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1102200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1436,11 +1456,11 @@
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
@@ -1457,38 +1477,41 @@
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-158500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>165000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-68100</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-153700</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,86 +1539,89 @@
       <c r="K15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="3">
         <v>914900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>680800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>182800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>646300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2002300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>721500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>654900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>649600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>342100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>986000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>536700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>690500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>728500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>719100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>677600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>656700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>553600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>495100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>516100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>486400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>511600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>538600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>518400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>509400</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK15" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,8 +1656,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1659,86 +1686,89 @@
       <c r="K17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="3">
         <v>14136300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14924500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12480500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15105000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12857400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8184400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6549000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5756600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3494900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4510700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3330500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5054200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6229300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6264600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5986700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5652000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6430200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5483700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5738100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1766,86 +1796,89 @@
       <c r="K18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M18" s="3">
         <v>1931700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3631200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3615800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2117400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1614200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>981100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1138400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1045300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1448200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-674600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>92700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>138500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>861500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1022900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1112900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>811000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1424200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>726600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>527000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>868500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>604800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>631700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,86 +1946,89 @@
       <c r="K20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="3">
         <v>33200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>61600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>489600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>293800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>139800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>218600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>219000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>212700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>84800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>57100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>52400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-51300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>131900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>144500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>227000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>161500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>88700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>154000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>176800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>90000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>25800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>225500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>113300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>149200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>118600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2019,86 +2056,89 @@
       <c r="K21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="3">
         <v>2967300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4417900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4634200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3069500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3876700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1947000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2046200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1926600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2091500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>816800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>738500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>862900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1752300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1906100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2063400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1644800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2102000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1385600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1233100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,86 +2166,89 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3">
         <v>118500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>111300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>120800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>103400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>90000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>105500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>80400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>81500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>70800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>73700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>68700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>81800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>85200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>95500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>90600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>89700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>82800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>77500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>94400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>70300</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH22" s="3">
         <v>80800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>69600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>68400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>74000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2233,86 +2276,89 @@
       <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M23" s="3">
         <v>1846400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3581400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3984600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2307900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1664100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1094100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1277000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1176500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1462200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-691200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>76400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>908200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1071900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1249300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>882800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1430100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>803000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>609400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>888300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>630600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>776400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,86 +2386,89 @@
       <c r="K24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M24" s="3">
         <v>1351300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2112800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1251300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1376400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>930200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>572900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>422100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>293100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-478800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-216900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>79600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>373600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>416500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>475300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>289500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>492100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>366600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>306300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>305200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>159300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>166100</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>193000</v>
       </c>
       <c r="AI24" s="3">
         <v>193000</v>
       </c>
       <c r="AJ24" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AK24" s="3">
         <v>120900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2574,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2554,86 +2606,89 @@
       <c r="K26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M26" s="3">
         <v>495100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1468700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2733300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>931400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>733900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>521200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>854900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>883400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1940900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-474300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>62200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-74200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>534700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>655400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>774100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>593300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>938000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>436400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>303000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>583000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>471200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>610400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>915500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2661,86 +2716,89 @@
       <c r="K27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M27" s="3">
         <v>341100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>900200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2118500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>594100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>583200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>300500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>658100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>691900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1875100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-505500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>26200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-173500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>414400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>520600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>638800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>423500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>719200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>244800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>222900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>445800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>348900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>491400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>798900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2875,8 +2936,8 @@
       <c r="K29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,86 +3266,89 @@
       <c r="K32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M32" s="3">
         <v>-33200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-61600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-489600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-293800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-139800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-218600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-219000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-212700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-84800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-57100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-52400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>51300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-131900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-144500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-227000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-161500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-88700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3303,86 +3376,89 @@
       <c r="K33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M33" s="3">
         <v>341100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>900200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2118500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>594100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>583200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>300500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>658100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>691900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1875100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-505500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>26200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-173500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>414400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>520600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>638800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>423500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>719200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>244800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>222900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>445800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>348900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>491400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>798900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,8 +3564,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3517,198 +3596,204 @@
       <c r="K35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M35" s="3">
         <v>341100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>900200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2118500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>594100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>583200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>300500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>658100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>691900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1875100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-505500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>26200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-173500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>414400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>520600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>638800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>423500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>719200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>244800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>222900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>445800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>348900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>491400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>798900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,971 +3871,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6142500</v>
+      </c>
+      <c r="E41" s="3">
         <v>6400200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6462200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5673400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8450700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7648900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8238800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6828600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10278100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8960500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8222000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7118400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6550400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5474700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4373300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3271300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3625800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2846600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7608800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6360000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3020700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3421700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3867300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4342100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4382900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4762400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3780200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3213800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1111900</v>
+        <v>1230000</v>
       </c>
       <c r="E42" s="3">
+        <v>879000</v>
+      </c>
+      <c r="F42" s="3">
         <v>1270400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1471100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1933300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1528700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2363500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2328600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2192500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4351800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8071700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8400100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8005200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5580900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>6690800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>9531500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3779200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3010200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3291200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5491600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6987300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3643500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2736600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3435100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2978500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3225800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4229900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2617600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>905400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>821300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3016900</v>
+        <v>2482700</v>
       </c>
       <c r="E43" s="3">
+        <v>3319200</v>
+      </c>
+      <c r="F43" s="3">
         <v>3074900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3180100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3680000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4100800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3286400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3037100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4332900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4783700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6224800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5761500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5860500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5014000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3793900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4157900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4349400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3343300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1941900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1843600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2862500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3564100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3807300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3585700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4357800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4056200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3196500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2945900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2420000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4075000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4278400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4103700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4099700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3900700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4236900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4423600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4377400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5354100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5751500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5589600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4256600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3414900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3245800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2706400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2507500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2345900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1541300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1538200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1572000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2153900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2370400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1909300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2075400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1858300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1845300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1639300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2099600</v>
+        <v>14071600</v>
       </c>
       <c r="E45" s="3">
+        <v>1940200</v>
+      </c>
+      <c r="F45" s="3">
         <v>3417400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3196200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3336900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3838800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1079600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2438900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2999800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1806500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1022300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>805200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>768200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>674300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>525500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>431700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>538500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>534600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>273000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>293500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>370900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>347900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>286600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>294100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>330200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>312300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>418700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>424900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>362300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>297300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>269300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>286100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>280500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>232400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26346700</v>
+      </c>
+      <c r="E46" s="3">
         <v>16703600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18503200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17624600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21500700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21116400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19205100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19056800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24180800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25256600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29292400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27674700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25440900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20158800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18629300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20098800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14800400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12080500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14656200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15526900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14813500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13131000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13068200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13566200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14124700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14214900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13470600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10841700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9086900</v>
+        <v>7556200</v>
       </c>
       <c r="E47" s="3">
+        <v>7671600</v>
+      </c>
+      <c r="F47" s="3">
         <v>9039700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8932800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8726900</v>
       </c>
-      <c r="H47" s="3">
-        <v>8032500</v>
-      </c>
       <c r="I47" s="3">
+        <v>8031400</v>
+      </c>
+      <c r="J47" s="3">
         <v>9185000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9433400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9563200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10292900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12286500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11576300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11807000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11509900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13968500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13733900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13026100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11737400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7767600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8480700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8646600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8831500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>9770500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6566700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6554000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6707000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5998800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5680000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16565100</v>
+      </c>
+      <c r="E48" s="3">
         <v>21147100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22432500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21307200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21557900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22196300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21475400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22336200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21075600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21395500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20763500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20747900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20447600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20130700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19727700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19286300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19232300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19153100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14920900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16464000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16726900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19237700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20358100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19369400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19616500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17879500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15679200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15670700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2094400</v>
+        <v>1225700</v>
       </c>
       <c r="E49" s="3">
+        <v>1438000</v>
+      </c>
+      <c r="F49" s="3">
         <v>2288600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2073300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2054200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1329700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2315800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2355900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2812900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2780100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2888700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2820400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2798600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3426800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3611900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3541100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3695600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3434000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3190500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4212000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4215300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4859900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5203800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4843200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5048000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3923700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3202100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3188600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>208100</v>
+        <v>184800</v>
       </c>
       <c r="E52" s="3">
+        <v>298200</v>
+      </c>
+      <c r="F52" s="3">
         <v>235300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>223900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>225500</v>
       </c>
-      <c r="H52" s="3">
-        <v>392400</v>
-      </c>
       <c r="I52" s="3">
+        <v>401200</v>
+      </c>
+      <c r="J52" s="3">
         <v>113300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>119000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>132600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3256300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3287500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3149000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3214200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3096200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3285600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3253400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4170600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2737900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2099700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2086900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1795600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1074000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>977500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>905800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>958200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>996000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1256000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1408700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>935700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53049100</v>
+      </c>
+      <c r="E54" s="3">
         <v>50536300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53789900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51417600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>55303700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>55999800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>53561600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>54568800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>59086300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62981500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68518500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>65968200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>63708300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58322400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>59223000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>59913500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>54925000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>49142900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>42634900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>46770600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46197900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>47134200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>49378100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>45251400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>46301300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>43721200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>39606700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36789600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2970200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3854400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3841200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3832600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4082400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4371600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4369200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4121200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4477400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5824900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6514500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5991100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6072700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5268700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4034100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4424600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4777900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4292800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2667400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2607300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3769100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4850600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4789700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4173900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5197500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5205900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4101400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3877000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1019200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1486700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1236900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1097200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1255800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1268900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1642700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1522900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1683000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1742300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1111000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2053200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1191500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1383300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1852300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1045300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1936100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1689600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>855200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>916400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>613100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>943300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1768900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1664600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1934300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>997200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>965800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1001400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>274900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>218800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>190700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>305200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4451800</v>
+        <v>8705100</v>
       </c>
       <c r="E59" s="3">
+        <v>3278800</v>
+      </c>
+      <c r="F59" s="3">
         <v>5093700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4839800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5877700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4458900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5114300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5109200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7136000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7940400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11723400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10918000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11148700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8175200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10021600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11731100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5604200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4606000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5440700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6826900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8336700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5174000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4881600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5518500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5219000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5247300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6182600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4643400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12694600</v>
+      </c>
+      <c r="E60" s="3">
         <v>9792900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10171800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9769600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11215900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11569600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11126200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10753300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13296400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15507500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19348900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18962300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18412800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14827200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15908000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17201000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12318300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10588400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8963300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10350600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12718900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10967800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11440200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11357000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12350800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11450500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11249900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9521900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7308700</v>
+      </c>
+      <c r="E61" s="3">
         <v>8252400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9092100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8247100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8621200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8821700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8440900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8885400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9507800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9648300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9987800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10084500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10854900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10382400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10311300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10897400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10944000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10215400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9427200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9955600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6896700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7957100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8107000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6550200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6260900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5806900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5052900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5035400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4907300</v>
+        <v>4930800</v>
       </c>
       <c r="E62" s="3">
+        <v>4852500</v>
+      </c>
+      <c r="F62" s="3">
         <v>5370300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5155900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5206600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5363100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4663400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5316600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4952200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8332500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9227000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8847300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9078000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9266900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9469200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9649000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9182400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8491900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7635800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8515600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8213500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8523300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9412800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8512400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8335100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8315800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6928000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6508900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26526200</v>
+      </c>
+      <c r="E66" s="3">
         <v>25050200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26881600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25274800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27110800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27958400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26534700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27278400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30055400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>41770900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46714300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45687100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45607700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>41513400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>42509600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>44194800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39133300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>35438600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29841700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32870200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32113100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>31943800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>33628400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30806400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>31501900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>29637600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26852700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24489800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15872200</v>
+      </c>
+      <c r="E72" s="3">
         <v>15037800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15848800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15053000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16529300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16397700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15536600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15520700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16823100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18378400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18769600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17224600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15043000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13671600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12888300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11960700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12032600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10195400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9106500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11379300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11564700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12445800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12920000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11727500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12038600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11306200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10196600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9765600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19136400</v>
+      </c>
+      <c r="E76" s="3">
         <v>18498800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18939300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18404600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20289100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20159200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19489800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19427900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20837700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21210500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21804200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20281100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18100500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16809000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16713500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15718700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15791700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13704300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12793200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13900400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14084700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15190300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15749700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14445000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14799400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14083600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12754000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12299800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,120 +7729,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7681,86 +7876,89 @@
       <c r="K81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M81" s="3">
         <v>341100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>900200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2118500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>594100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>583200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>300500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>658100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>691900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1875100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-505500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>26200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-173500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>414400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>520600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>638800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>423500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>719200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>244800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>222900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>445800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>348900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>491400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>798900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>670000</v>
+      </c>
+      <c r="E83" s="3">
         <v>446600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>710200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>655000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>696400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>416800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>702100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>660700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>662100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1002400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>725100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>528800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>658300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2122700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>747400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>688800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>668700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>558500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1434400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>593500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>775600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>758800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>738700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>723500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>672300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>589100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>505100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>529200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>494100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>596900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>548700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>584600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>500400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1466700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1066400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1584900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1266500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1966800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1207000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1804600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>246700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2918300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1592700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3438800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>503800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2910700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3017100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1731700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1652600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1125700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>677200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>822000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>592400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1225100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1145200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1316900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1334000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1035900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1318900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1075500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1353800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>832500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>888600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>718400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1013800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1063300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-988200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-842200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-878200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-879300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1046800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-911300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-896300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-932200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-910000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-735000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-651000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-647000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-758000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-579000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-657000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-570300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-562500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-402700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-462500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-637100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-706300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-665200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-578800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-619600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-671900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1124100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-389300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1315000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-832500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-884700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1110900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-265700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-859200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1069100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-967200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1115300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-499800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-641800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-118500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-688800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-440100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-472400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-699300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-744800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-488200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-886000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-495100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>379200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>445400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9286,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>48700</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3">
         <v>36800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1782900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3">
         <v>34900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1819900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>624700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-303700</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-91100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-35500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-451800</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-240000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>115600</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-908200</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>85200</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-760900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>59500</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-385100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>291100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3150100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-87400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-952800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-117500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2938900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-115200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1305500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-527700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-66800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>203100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-687200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1201900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3212700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-661100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-640900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1214000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-818800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-275100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>288600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>886400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>191300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-18200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-71100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-18800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-68600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-24900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-41500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7900</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-11200</v>
       </c>
       <c r="AH101" s="3">
         <v>-11200</v>
       </c>
       <c r="AI101" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>344800</v>
+      </c>
+      <c r="E102" s="3">
         <v>300200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>552100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2718300</v>
       </c>
-      <c r="G102" s="3">
-        <v>996900</v>
-      </c>
       <c r="H102" s="3">
+        <v>995800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-863300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1417200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3559000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1725300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>520600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1171500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>583200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1055500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1073300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1018700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-356500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>630600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1558900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3333800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-176700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-255700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-654100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>32900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-434200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>723900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>527200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>350300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>493700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>796600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>663200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>496500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>OMVKY</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -842,86 +846,89 @@
       <c r="L8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="3">
         <v>16068000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18555600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16096300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17222400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14471700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9165500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7687400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6801900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4943100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3836100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3423300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5192700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7090800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7287500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7099600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6463100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7854500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6210300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6265200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -952,86 +959,89 @@
       <c r="L9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3">
         <v>12383000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12835500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11628500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10985500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9568300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6578800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5091100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4397000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3634500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2510700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2211300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3708000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4687200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4695400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4537400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4302700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5203600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4239900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4662100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1062,86 +1072,89 @@
       <c r="L10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="3">
         <v>3685000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5720100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4467700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6237000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4903400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2586700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2596300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2404800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1308600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1325400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1212000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1484700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2403700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2592100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2562200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2160300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2650900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1970400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1603100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1212,86 +1226,89 @@
       <c r="L12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
         <v>117400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>60500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>84900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>164800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>48500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>47600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>40200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>43900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>674600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>90500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>129800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>85200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>46500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>83500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>55000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>71000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>27700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>58200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>40600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>107700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>39300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>65100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>35900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>83300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,21 +1452,21 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>6500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-171900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1102200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1459,11 +1479,11 @@
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
@@ -1480,38 +1500,41 @@
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-158500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>165000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-68100</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-153700</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1542,86 +1565,89 @@
       <c r="L15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="3">
         <v>914900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>680800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>182800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>646300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2002300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>721500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>654900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>649600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>342100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>986000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>536700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>690500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>728500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>719100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>677600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>656700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>553600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>495100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>516100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>486400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>511600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>538600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>518400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>509400</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AL15" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,8 +1683,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1689,86 +1716,89 @@
       <c r="L17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" s="3">
         <v>14136300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14924500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12480500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15105000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12857400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8184400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6549000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5756600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3494900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4510700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3330500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5054200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6229300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6264600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5986700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5652000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6430200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5483700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5738100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1799,86 +1829,89 @@
       <c r="L18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="3">
         <v>1931700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3631200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3615800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2117400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1614200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>981100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1138400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1045300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1448200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-674600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>92700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>138500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>861500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1022900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1112900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>811000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1424200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>726600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>527000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>868500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>604800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>631700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,86 +1983,89 @@
       <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" s="3">
         <v>33200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>61600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>489600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>293800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>139800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>218600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>219000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>212700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>84800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>57100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>52400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-51300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>131900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>144500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>227000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>161500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>88700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>154000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>176800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>90000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>25800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>225500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>113300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>149200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>118600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2059,86 +2096,89 @@
       <c r="L21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" s="3">
         <v>2967300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4417900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4634200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3069500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3876700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1947000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2046200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1926600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2091500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>816800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>738500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>862900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1752300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1906100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2063400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1644800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2102000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1385600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1233100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,86 +2209,89 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3">
         <v>118500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>111300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>120800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>103400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>90000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>105500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>80400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>81500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>70800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>73700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>68700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>81800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>85200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>95500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>90600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>89700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>82800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>77500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>94400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>70300</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI22" s="3">
         <v>80800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>69600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>68400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>74000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2279,86 +2322,89 @@
       <c r="L23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3">
         <v>1846400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3581400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3984600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2307900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1664100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1094100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1277000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1176500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1462200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-691200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>76400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>908200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1071900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1249300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>882800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1430100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>803000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>609400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>888300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>630600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>776400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,86 +2435,89 @@
       <c r="L24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N24" s="3">
         <v>1351300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2112800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1251300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1376400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>930200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>572900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>422100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>293100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-478800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-216900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>79600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>373600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>416500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>475300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>289500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>492100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>366600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>306300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>305200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>159300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>166100</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>193000</v>
       </c>
       <c r="AJ24" s="3">
         <v>193000</v>
       </c>
       <c r="AK24" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AL24" s="3">
         <v>120900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,8 +2626,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2609,86 +2661,89 @@
       <c r="L26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N26" s="3">
         <v>495100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1468700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2733300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>931400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>733900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>521200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>854900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>883400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1940900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-474300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>62200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-74200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>534700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>655400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>774100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>593300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>938000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>436400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>303000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>583000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>471200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>610400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>915500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2719,86 +2774,89 @@
       <c r="L27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" s="3">
         <v>341100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>900200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2118500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>594100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>583200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>658100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>691900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1875100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-505500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>26200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-173500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>414400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>520600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>638800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>423500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>719200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>244800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>222900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>445800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>348900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>491400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>798900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2939,8 +3000,8 @@
       <c r="L29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,86 +3339,89 @@
       <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="3">
         <v>-33200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-61600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-489600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-293800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-139800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-218600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-219000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-212700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-84800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-57100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-52400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>51300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-131900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-144500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-227000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-161500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-88700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3379,86 +3452,89 @@
       <c r="L33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N33" s="3">
         <v>341100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>900200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2118500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>594100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>583200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>658100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>691900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1875100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-505500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>26200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-173500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>414400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>520600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>638800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>423500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>719200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>244800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>222900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>445800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>348900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>491400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>798900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,8 +3643,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3599,201 +3678,207 @@
       <c r="L35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N35" s="3">
         <v>341100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>900200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2118500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>594100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>583200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>658100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>691900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1875100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-505500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>26200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-173500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>414400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>520600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>638800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>423500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>719200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>244800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>222900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>445800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>348900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>491400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>798900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,998 +3958,1026 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6178500</v>
+      </c>
+      <c r="E41" s="3">
         <v>6142500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6400200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6462200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5673400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8450700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7648900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8238800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6828600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10278100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8960500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8222000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7118400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6550400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5474700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4373300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3271300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3625800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2846600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7608800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6360000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3020700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3421700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3867300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4342100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4382900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4762400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3780200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3213800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1327100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1230000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>879000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1270400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1471100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1933300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1528700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2363500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2328600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2192500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4351800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8071700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8400100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8005200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5580900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>6690800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>9531500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3779200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3010200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3291200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5491600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>6987300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3643500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2736600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3435100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2978500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3225800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4229900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2617600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>905400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>821300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2293600</v>
+      </c>
+      <c r="E43" s="3">
         <v>2482700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3319200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3074900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3180100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3680000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4100800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3286400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3037100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4332900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4783700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6224800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5761500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5860500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5014000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3793900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4157900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4349400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3343300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1941900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1843600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2862500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3564100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3807300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3585700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4357800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4056200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3196500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2945900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2456800</v>
+      </c>
+      <c r="E44" s="3">
         <v>2420000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4075000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4278400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4103700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4099700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3900700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4236900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4423600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4377400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5354100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5751500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5589600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4256600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3414900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3245800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2706400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2507500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2345900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1541300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1538200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1572000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2153900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2370400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1909300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2075400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1858300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1845300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1639300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13616000</v>
+      </c>
+      <c r="E45" s="3">
         <v>14071600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1940200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3417400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3196200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3336900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3838800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1079600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2438900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2999800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1806500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1022300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>805200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>768200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>674300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>525500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>431700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>538500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>534600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>273000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>293500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>370900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>347900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>286600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>294100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>330200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>312300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>418700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>424900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>362300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>297300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>269300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>286100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>280500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>232400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25872000</v>
+      </c>
+      <c r="E46" s="3">
         <v>26346700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16703600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18503200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17624600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21500700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21116400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19205100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19056800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24180800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25256600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29292400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27674700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25440900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20158800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18629300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>20098800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14800400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12080500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14656200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15526900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14813500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13131000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13068200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13566200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14124700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14214900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13470600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10841700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7463300</v>
+      </c>
+      <c r="E47" s="3">
         <v>7556200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7671600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9039700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8932800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8726900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8031400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9185000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9433400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9563200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10292900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12286500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11576300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11807000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11509900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13968500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13733900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13026100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11737400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7767600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8480700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8646600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8831500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>9770500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6566700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6554000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6707000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5998800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5680000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17862600</v>
+      </c>
+      <c r="E48" s="3">
         <v>16565100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21147100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22432500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21307200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21557900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22196300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21475400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22336200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21075600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21395500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20763500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20747900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20447600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20130700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19727700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19286300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19232300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19153100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14920900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16464000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16726900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19237700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20358100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19369400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19616500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17879500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15679200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15670700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1323500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1225700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1438000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2288600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2073300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2054200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1329700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2315800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2355900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2812900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2780100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2888700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2820400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2798600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3426800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3611900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3541100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3695600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3434000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3190500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4212000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4215300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4859900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5203800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4843200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5048000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3923700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3202100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3188600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E52" s="3">
         <v>184800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>298200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>235300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>223900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>225500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>401200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>113300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>119000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>132600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3256300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3287500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3149000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3214200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3096200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3285600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3253400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4170600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2737900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2099700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2086900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1795600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1074000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>977500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>905800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>958200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>996000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1256000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1408700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>935700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54001200</v>
+      </c>
+      <c r="E54" s="3">
         <v>53049100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>50536300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53789900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>51417600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>55303700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>55999800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53561600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>54568800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>59086300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>62981500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>68518500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65968200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>63708300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58322400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>59223000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>59913500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>54925000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49142900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42634900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46770600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>46197900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>47134200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>49378100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>45251400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>46301300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>43721200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39606700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>36789600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3208500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2970200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3854400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3841200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3832600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4082400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4371600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4369200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4121200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4477400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5824900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6514500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5991100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6072700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5268700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4034100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4424600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4777900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4292800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2667400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2607300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3769100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4850600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4789700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4173900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5197500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5205900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4101400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3877000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>975900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1019200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1486700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1236900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1097200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1255800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1268900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1642700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1522900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1683000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1742300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1111000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2053200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1191500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1383300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1852300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1045300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1936100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1689600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>855200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>916400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>613100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>943300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1768900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1664600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1934300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>997200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>965800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1001400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>274900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>218800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>190700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>305200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8156200</v>
+      </c>
+      <c r="E59" s="3">
         <v>8705100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3278800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5093700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4839800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5877700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4458900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5114300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5109200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7136000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7940400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11723400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10918000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11148700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8175200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10021600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11731100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5604200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4606000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5440700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6826900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8336700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5174000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4881600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5518500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5219000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5247300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6182600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4643400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12340600</v>
+      </c>
+      <c r="E60" s="3">
         <v>12694600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9792900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10171800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9769600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11215900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11569600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11126200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10753300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13296400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15507500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19348900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18962300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18412800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14827200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>15908000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17201000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12318300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10588400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8963300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10350600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12718900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10967800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11440200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11357000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12350800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11450500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11249900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9521900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7881400</v>
+      </c>
+      <c r="E61" s="3">
         <v>7308700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8252400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9092100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8247100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8621200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8821700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8440900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8885400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9507800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9648300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9987800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10084500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10854900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10382400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10311300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10897400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10944000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10215400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9427200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9955600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6896700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7957100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8107000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6550200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6260900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5806900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5052900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5035400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5270700</v>
+      </c>
+      <c r="E62" s="3">
         <v>4930800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4852500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5370300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5155900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5206600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5363100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4663400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5316600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4952200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8332500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9227000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8847300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9078000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9266900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9469200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9649000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9182400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8491900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7635800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8515600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8213500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8523300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9412800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8512400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8335100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8315800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6928000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6508900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27122700</v>
+      </c>
+      <c r="E66" s="3">
         <v>26526200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25050200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26881600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25274800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27110800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27958400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26534700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27278400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30055400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41770900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46714300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45687100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45607700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41513400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>42509600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>44194800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>39133300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35438600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29841700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32870200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>32113100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>31943800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33628400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>30806400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>31501900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29637600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26852700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24489800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15722800</v>
+      </c>
+      <c r="E72" s="3">
         <v>15872200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15037800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15848800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15053000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16529300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16397700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15536600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15520700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16823100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18378400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18769600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17224600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15043000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13671600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12888300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11960700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12032600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10195400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9106500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11379300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11564700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12445800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12920000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11727500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12038600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11306200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10196600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9765600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19355300</v>
+      </c>
+      <c r="E76" s="3">
         <v>19136400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18498800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18939300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18404600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20289100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20159200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19489800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19427900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20837700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21210500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21804200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20281100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18100500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16809000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16713500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15718700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15791700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13704300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12793200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13900400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14084700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15190300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15749700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14445000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14799400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14083600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12754000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12299800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,123 +7921,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7879,86 +8074,89 @@
       <c r="L81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N81" s="3">
         <v>341100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>900200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2118500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>594100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>583200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>658100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>691900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1875100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-505500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>26200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-173500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>414400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>520600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>638800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>423500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>719200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>244800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>222900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>445800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>348900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>491400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>798900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>669700</v>
+      </c>
+      <c r="E83" s="3">
         <v>670000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>446600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>710200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>655000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>696400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>416800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>702100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>660700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>662100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1002400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>725100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>528800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>658300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2122700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>747400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>688800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>668700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>558500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1434400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>593500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>775600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>758800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>738700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>723500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>672300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>589100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>505100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>529200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>494100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>596900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>548700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>584600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>500400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1466700</v>
+        <v>1271900</v>
       </c>
       <c r="E89" s="3">
+        <v>1467800</v>
+      </c>
+      <c r="F89" s="3">
         <v>1066400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1584900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1266500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1966800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1207000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1804600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>246700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2918300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1592700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3438800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>503800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2910700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3017100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1731700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1652600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1125700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>677200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>822000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>592400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1225100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1145200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1316900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1334000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1035900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1318900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1075500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1353800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>832500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>888600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>718400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1133300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1013800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1063300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-988200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-842200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-879300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1046800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-911300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-896300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-932200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-910000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-735000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-651000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-647000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-758000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-579000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-657000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-570300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-562500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-402700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-462500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-637100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-706300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-665200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-578800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-619600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-671900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1124100</v>
+        <v>138600</v>
       </c>
       <c r="E94" s="3">
+        <v>-1125200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-389300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1315000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-832500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-884700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1110900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-265700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-859200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1069100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-967200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1115300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-499800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-641800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-118500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-688800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-440100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-472400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-699300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-744800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-488200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-886000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-495100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>379200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>445400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9520,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
+        <v>1823800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3">
         <v>36800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1782900</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
         <v>34900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1819900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>624700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-303700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-91100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-35500</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-451800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-240000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>115600</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-908200</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>85200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-760900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>59500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1987100</v>
+      </c>
+      <c r="E100" s="3">
         <v>7600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-385100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>291100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3150100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-87400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-952800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-117500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2938900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-115200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1305500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-527700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-66800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>203100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-687200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1201900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3212700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-661100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-640900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1214000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-818800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-275100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>288600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>886400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>191300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-18200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-71100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-18800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-68600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-10800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-9500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-24900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-41500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-7900</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-11200</v>
       </c>
       <c r="AI101" s="3">
         <v>-11200</v>
       </c>
       <c r="AJ101" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-621300</v>
+      </c>
+      <c r="E102" s="3">
         <v>344800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>552100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2718300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>995800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-863300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1417200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3559000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1725300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>520600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1171500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>583200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1055500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1073300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1018700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-356500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>630600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1558900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3333800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-176700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-255700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-654100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>32900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-434200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>723900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>527200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>350300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>493700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>796600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>663200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>496500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
   <si>
     <t>OMVKY</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,86 +863,92 @@
       <c r="N8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="3">
         <v>16068000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>18555600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>16096300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>17222400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>14471700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9165500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7687400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>6801900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>4943100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3836100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3423300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5192700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>7090800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>7287500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7099600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>6463100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>7854500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>6210300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>6265200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,86 +985,92 @@
       <c r="N9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="3">
         <v>12383000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>12835500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>11628500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>10985500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>9568300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>6578800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>5091100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4397000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3634500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2510700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2211300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>3708000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>4687200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>4695400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>4537400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>4302700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>5203600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>4239900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>4662100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1088,86 +1107,92 @@
       <c r="N10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="3">
         <v>3685000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>5720100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4467700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>6237000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4903400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2586700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2596300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2404800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1308600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1325400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1212000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1484700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2403700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2592100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2562200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2160300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>2650900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1970400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1603100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1233,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1246,86 +1273,92 @@
       <c r="N12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3">
         <v>117400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>60500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>84900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>10900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>164800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>48500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>47600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>40200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>43900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>674600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>90500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>129800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>85200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>46500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>83500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>55000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>71000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>27700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>58200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>40600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>39300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>65100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>35900</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>83300</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1440,8 +1473,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1478,24 +1517,24 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>6500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-171900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>1102200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1505,14 +1544,14 @@
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
@@ -1526,38 +1565,44 @@
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-158500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>165000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>-68100</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>-153700</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,86 +1639,92 @@
       <c r="N15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="3">
         <v>914900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>680800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>182800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>646300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2002300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>721500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>654900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>649600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>342100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>986000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>536700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>690500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>728500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>719100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>677600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>656700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>553600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>495100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>516100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>486400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>511600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>538600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>518400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>509400</v>
       </c>
-      <c r="AM15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN15" s="3" t="s">
+      <c r="AO15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,8 +1762,10 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1749,86 +1802,92 @@
       <c r="N17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="3">
         <v>14136300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>14924500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>12480500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>15105000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>12857400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>8184400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6549000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5756600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3494900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4510700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3330500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5054200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6229300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6264600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>5986700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>5652000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6430200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>5483700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>5738100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1865,86 +1924,92 @@
       <c r="N18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="3">
         <v>1931700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3631200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>3615800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2117400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1614200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>981100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1138400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1045300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1448200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-674600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>92700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>138500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>861500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1022900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1112900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>811000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>1424200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>726600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>527000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>868500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>604800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>631700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2050,10 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,86 +2090,92 @@
       <c r="N20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="3">
         <v>33200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>61600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>489600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>293800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>139800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>218600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>219000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>212700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>84800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>57100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>52400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-51300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>131900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>144500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>227000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>161500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>88700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>154000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>176800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>90000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>25800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>225500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>113300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>149200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>118600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2139,86 +2212,92 @@
       <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="3">
         <v>2967300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>4417900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4634200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3069500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>3876700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1947000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2046200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1926600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2091500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>816800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>738500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>862900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1752300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1906100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>2063400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1644800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>2102000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1385600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1233100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2255,86 +2334,92 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="3">
         <v>118500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>111300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>120800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>103400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>90000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>105500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>80400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>81500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>70800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>73700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>68700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>81800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>85200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>95500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>90600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>89700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>82800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>77500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>94400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>70300</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL22" s="3">
         <v>80800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>69600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>68400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>74000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2371,86 +2456,92 @@
       <c r="N23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1846400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3581400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3984600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2307900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1664100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1094100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1277000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1176500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1462200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-691200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>76400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>5500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>908200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1071900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1249300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>882800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>1430100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>803000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>609400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>888300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>630600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>776400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,86 +2578,92 @@
       <c r="N24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1351300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2112800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1251300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1376400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>930200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>572900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>422100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>293100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-478800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-216900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>14200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>79600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>373600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>416500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>475300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>289500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>492100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>366600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>306300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>305200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>159300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>166100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>193000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>193000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>120900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2778,14 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2719,86 +2822,92 @@
       <c r="N26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="3">
         <v>495100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1468700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2733300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>931400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>733900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>521200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>854900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>883400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1940900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-474300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>62200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>534700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>655400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>774100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>593300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>938000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>436400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>303000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>583000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>471200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>610400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>915500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2835,86 +2944,92 @@
       <c r="N27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="3">
         <v>341100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>900200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2118500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>594100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>583200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>300500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>658100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>691900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1875100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-505500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>26200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-173500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>414400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>520600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>638800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>423500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>719200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>244800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>222900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>445800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>491400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>798900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3067,11 +3188,11 @@
       <c r="N29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3510,14 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,86 +3554,92 @@
       <c r="N32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-33200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-61600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-489600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-293800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-139800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-218600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-219000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-212700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-84800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-57100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-52400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>51300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-131900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-144500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-227000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-161500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-88700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3531,86 +3676,92 @@
       <c r="N33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="3">
         <v>341100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>900200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2118500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>594100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>583200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>300500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>658100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>691900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1875100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-505500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>26200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-173500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>414400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>520600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>638800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>423500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>719200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>244800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>222900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>445800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>491400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>798900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3876,14 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3763,207 +3920,219 @@
       <c r="N35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="3">
         <v>341100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>900200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2118500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>594100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>583200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>300500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>658100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>691900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1875100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-505500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>26200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-173500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>414400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>520600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>638800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>423500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>719200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>244800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>222900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>445800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>491400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>798900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,1052 +4217,1108 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4042400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5961000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5217600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6178500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6142500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6400200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6462200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5673400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8450700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7648900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8238800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6828600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10278100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8960500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8222000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7118400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6550400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>5474700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4373300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3271300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3625800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2846600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>7608800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>6360000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3020700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3421700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3867300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4342100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>4382900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>4762400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3780200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>3213800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1972800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1020300</v>
+      </c>
+      <c r="F42" s="3">
         <v>1459600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1327100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1230000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>879000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1270400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1471100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1933300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1528700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2363500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2328600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2192500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>4351800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>8071700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>8400100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>8005200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>5580900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>6690800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>9531500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>3779200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>3010200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>3291200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>5491600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>6987300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>3643500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>2736600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>3435100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>2978500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>3225800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>4229900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>2617600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>905400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>821300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2804100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2411600</v>
+      </c>
+      <c r="F43" s="3">
         <v>2390000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2293600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2482700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3319200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3074900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3180100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3680000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4100800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3286400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3037100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4332900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4783700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>6224800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5761500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5860500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5014000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3793900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>4157900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4349400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3343300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1941900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1843600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2862500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>3564100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3807300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>3585700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>4357800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>4056200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3196500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>2945900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2533100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2303600</v>
+      </c>
+      <c r="F44" s="3">
         <v>2750200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2456800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2420000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>4075000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>4278400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>4103700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>4099700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3900700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>4236900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>4423600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4377400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>5354100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5751500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>5589600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>4256600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3414900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3245800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2706400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2507500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2345900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1541300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1538200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1572000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>2153900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>2370400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1909300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>2075400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1858300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1845300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1639300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>13891000</v>
+      </c>
+      <c r="F45" s="3">
         <v>12994300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>13616000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14071600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1940200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3417400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3196200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3336900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3838800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1079600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2438900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2999800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1806500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1022300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>805200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>768200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>674300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>525500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>431700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>538500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>534600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>273000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>293500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>370900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>347900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>286600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>294100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>330200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>312300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>418700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>424900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>362300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>297300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>269300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>286100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>280500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>232400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12731500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>25656900</v>
+      </c>
+      <c r="F46" s="3">
         <v>24811700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>25872000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>26346700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>16703600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18503200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>17624600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>21500700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>21116400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>19205100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>19056800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>24180800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>25256600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>29292400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>27674700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>25440900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>20158800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>18629300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>20098800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>14800400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>12080500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>14656200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>15526900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>14813500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>13131000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>13068200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>13566200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>14124700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>14214900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>13470600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>10841700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15409900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6307400</v>
+      </c>
+      <c r="F47" s="3">
         <v>7436300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>7463300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>7556200</v>
       </c>
-      <c r="G47" s="3">
-        <v>7671600</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
+        <v>7070100</v>
+      </c>
+      <c r="J47" s="3">
         <v>9039700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>8932800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>8726900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>8031400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>9185000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>9433400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>9563200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>10292900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>12286500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>11576300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>11807000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>11509900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>13968500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>13733900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>13026100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>11737400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>7767600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>8480700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>8646600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>8831500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>9770500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>6566700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>6554000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>6707000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>5998800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>5680000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18348900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>18456000</v>
+      </c>
+      <c r="F48" s="3">
         <v>18314000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>17862600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>16565100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>21147100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>22432500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>21307200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>21557900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>22196300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>21475400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>22336200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>21075600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>21395500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>20763500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>20747900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>20447600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>20130700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>19727700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>19286300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>19232300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>19153100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>14920900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>16464000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>16726900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>19237700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>20358100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>19369400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>19616500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>17879500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>15679200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>15670700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1237200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>955700</v>
+      </c>
+      <c r="F49" s="3">
         <v>1312900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1323500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1225700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1438000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2288600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2073300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2054200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1329700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2315800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2355900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2812900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2780100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2888700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2820400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2798600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3426800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3611900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3541100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3695600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3434000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3190500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4212000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4215300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4859900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>5203800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>4843200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>5048000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>3923700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>3202100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>3188600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5555,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>319400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>693900</v>
+      </c>
+      <c r="F52" s="3">
         <v>265200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>216100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>184800</v>
       </c>
-      <c r="G52" s="3">
-        <v>298200</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>899700</v>
+      </c>
+      <c r="J52" s="3">
         <v>235300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>223900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>225500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>401200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>113300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>119000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>132600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3256300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3287500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3149000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3214200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3096200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3285600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3253400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>4170600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2737900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2099700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2086900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1795600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1074000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>977500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>905800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>958200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>996000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1256000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1408700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>935700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49625300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>54406500</v>
+      </c>
+      <c r="F54" s="3">
         <v>53404900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>54001200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>53049100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>50536300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>53789900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>51417600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>55303700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>55999800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>53561600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>54568800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>59086300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>62981500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>68518500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>65968200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>63708300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>58322400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>59223000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>59913500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>54925000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>49142900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>42634900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>46770600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>46197900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>47134200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>49378100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>45251400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>46301300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>43721200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>39606700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>36789600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +6013,742 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3389800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3091500</v>
+      </c>
+      <c r="F57" s="3">
         <v>3358000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3208500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2970200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3854400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3841200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3832600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4082400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4371600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4369200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4121200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4477400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5824900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6514500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5991100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6072700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5268700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4034100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4424600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4777900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4292800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2667400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2607300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3769100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>4850600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>4789700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>4173900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>5197500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>5205900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>4101400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>3877000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1696100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1662600</v>
+      </c>
+      <c r="F58" s="3">
         <v>504500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>975900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1019200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1486700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1236900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1097200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1255800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1268900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1642700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1522900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1683000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1742300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1111000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2053200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1191500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1383300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1852300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1045300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1936100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1689600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>855200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>916400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>613100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>943300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1768900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1664600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1934300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>997200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>965800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1001400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>274900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>218800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>190700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>305200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4719200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7297200</v>
+      </c>
+      <c r="F59" s="3">
         <v>8242400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8156200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>8705100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3278800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5093700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4839800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5877700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4458900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5114300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5109200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>7136000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>7940400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11723400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>10918000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>11148700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>8175200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>10021600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>11731100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5604200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>4606000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>5440700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>6826900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>8336700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>5174000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>4881600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>5518500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>5219000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>5247300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>6182600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>4643400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9805100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12956400</v>
+      </c>
+      <c r="F60" s="3">
         <v>12104900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>12340600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12694600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9792900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10171800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9769600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11215900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11569600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11126200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10753300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>13296400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>15507500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>19348900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>18962300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>18412800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>14827200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>15908000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>17201000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>12318300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10588400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>8963300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>10350600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>12718900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>10967800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>11440200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>11357000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>12350800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>11450500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>11249900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>9521900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7539500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7726900</v>
+      </c>
+      <c r="F61" s="3">
         <v>7708600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7881400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7308700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8252400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9092100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>8247100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8621200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8821700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8440900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8885400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9507800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9648300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9987800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10084500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>10854900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>10382400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>10311300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>10897400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>10944000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>10215400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>9427200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>9955600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>6896700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>7957100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>8107000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>6550200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>6260900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>5806900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>5052900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>5035400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5744300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5674500</v>
+      </c>
+      <c r="F62" s="3">
         <v>5525000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>5270700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4930800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4852500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5370300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5155900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>5206600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5363100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4663400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5316600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4952200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>8332500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>9227000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8847300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>9078000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>9266900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>9469200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>9649000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>9182400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>8491900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>7635800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>8515600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>8213500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>8523300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>9412800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>8512400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>8335100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>8315800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>6928000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>6508900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24639700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>27911200</v>
+      </c>
+      <c r="F66" s="3">
         <v>26942400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>27122700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>26526200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>25050200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>26881600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>25274800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>27110800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>27958400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>26534700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>27278400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>30055400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>41770900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>46714300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>45687100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>45607700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>41513400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>42509600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>44194800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>39133300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>35438600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>29841700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>32870200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>32113100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>31943800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>33628400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>30806400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>31501900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>29637600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>26852700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>24489800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17890000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>16469400</v>
+      </c>
+      <c r="F72" s="3">
         <v>16281800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>15722800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>15872200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>15037800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>15848800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>15053000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>16529300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>16397700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>15536600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>15520700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>16823100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>18378400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>18769600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>17224600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>15043000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>13671600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>12888300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>11960700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>12032600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>10195400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>9106500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>11379300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>11564700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>12445800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>12920000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>11727500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>12038600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>11306200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>10196600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>9765600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20665300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>19174600</v>
+      </c>
+      <c r="F76" s="3">
         <v>19033200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>19355300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>19136400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>18498800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>18939300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>18404600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20289100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20159200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19489800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19427900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>20837700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>21210500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>21804200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>20281100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>18100500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>16809000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>16713500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>15718700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15791700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>13704300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>12793200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>13900400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>14084700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>15190300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>15749700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>14445000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>14799400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>14083600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>12754000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>12299800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8493,141 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8275,86 +8664,92 @@
       <c r="N81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q81" s="3">
         <v>341100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>900200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2118500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>594100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>583200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>300500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>658100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>691900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1875100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-505500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>26200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-173500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>414400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>520600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>638800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>423500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>719200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>244800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>222900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>445800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>491400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>798900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8790,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>528500</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="3">
         <v>710500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>670700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>670000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>446600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>710200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>656100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>696400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>416800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>702100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>660700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>662100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1002400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>725100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>528800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>658300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2122700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>747400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>688800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>668700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>558500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1434400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>593500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>775600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>758800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>738700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>723500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>672300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>589100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>505100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>529200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>494100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>596900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>548700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>584600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>500400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>894700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1973700</v>
+      </c>
+      <c r="F89" s="3">
         <v>1283600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1271900</v>
       </c>
-      <c r="F89" s="3">
-        <v>1467800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>1066400</v>
-      </c>
       <c r="H89" s="3">
+        <v>1466700</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J89" s="3">
         <v>1584900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1266500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1966800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1207000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1804600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>246700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>2918300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1592700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3438800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>503800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2910700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>3017100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1731700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1652600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1125700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>677200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>822000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>592400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1225100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1145200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1316900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1334000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1035900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1318900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1075500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1353800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>832500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>888600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>718400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9688,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1071100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1194100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1091200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1133300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1013800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1063300</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J91" s="3">
         <v>-988200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-841100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-879300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1046800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-911300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-896300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-932200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-910000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-735000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-651000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-647000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-758000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-579000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-657000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-570300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-562500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-402700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-462500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-637100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-706300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-665200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-578800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-619600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-671900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10050,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3366800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-921700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1228400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>138600</v>
       </c>
-      <c r="F94" s="3">
-        <v>-1125200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-389300</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1124100</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1315000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-832500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-884700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1110900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-265700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-859200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1069100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-967200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>1115300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-499800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-641800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-118500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-688800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-440100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-472400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-699300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-744800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-488200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-886000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-495100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>379200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>445400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,124 +10220,132 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F96" s="3">
         <v>75100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1823800</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3">
         <v>36800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1782900</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N96" s="3">
         <v>34900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1819900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>624700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-303700</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-91100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-35500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-451800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-240000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>115600</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-908200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>85200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-760900</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>59500</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10704,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-124500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>304100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1652000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1987100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>7600</v>
       </c>
-      <c r="G100" s="3">
-        <v>-385100</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J100" s="3">
         <v>291100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-3150100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-87400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-952800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-117500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2938900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-115200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-13300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1305500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-527700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-66800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>203100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-687200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1201900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>3212700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-661100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-640900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>1214000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-818800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-275100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>288600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>886400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>191300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-7600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-8700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-18200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>4900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-71100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-18800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>5400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>3300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-68600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-10800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-4300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-9500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-5000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-24900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-41500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>5900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>2400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-11200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2594300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1347900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1600400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-621300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>344800</v>
       </c>
-      <c r="G102" s="3">
-        <v>300200</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>552100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2717200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>995800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-863300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1417200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3559000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1725300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>520600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1171500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>583200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1055500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1073300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1018700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-356500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>630600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1558900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3333800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-176700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-255700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-654100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>32900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-434200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>723900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>527200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>350300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>493700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>796600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>663200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>496500</v>
       </c>
     </row>
